--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_48.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5978283.905271458</v>
+        <v>5978242.945075627</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12885492.60650516</v>
+        <v>12891796.28327284</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12885492.60650516</v>
+        <v>12891796.28327284</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>795350.9925644388</v>
+        <v>796539.5137032263</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>795350.9925644388</v>
+        <v>796539.5137032263</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37521205.65533291</v>
+        <v>37518382.03818937</v>
       </c>
     </row>
   </sheetData>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.99931295557451</v>
+        <v>72.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>37.62546667252622</v>
+        <v>40.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>2.339155739849787</v>
+        <v>1.339155739849787</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -705,25 +705,25 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>81.7181175510666</v>
+        <v>80.7181175510666</v>
       </c>
       <c r="T2" t="n">
-        <v>177.6900942913779</v>
+        <v>176.6900942913779</v>
       </c>
       <c r="U2" t="n">
-        <v>241.2032864983594</v>
+        <v>240.2032864983594</v>
       </c>
       <c r="V2" t="n">
-        <v>221.8510241668239</v>
+        <v>219.240312596356</v>
       </c>
       <c r="W2" t="n">
-        <v>230.3734759809475</v>
+        <v>229.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>184.2818334606677</v>
+        <v>183.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>103.3174326828064</v>
+        <v>102.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -739,13 +739,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.6190830448386</v>
@@ -778,28 +778,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>157.703566977272</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>131.7951557829454</v>
+        <v>130.7951557829454</v>
       </c>
       <c r="S3" t="n">
-        <v>56.32664147404529</v>
+        <v>55.32664147404529</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>72.85363317840789</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.510667191520156</v>
+        <v>5.510667191520156</v>
       </c>
       <c r="W3" t="n">
-        <v>284.0221908942289</v>
+        <v>23.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>349</v>
+        <v>10.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -842,25 +842,25 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5341199610573764</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>96.80197205828756</v>
+        <v>95.05458694706036</v>
       </c>
       <c r="N4" t="n">
-        <v>147.7318293700456</v>
+        <v>146.7318293700456</v>
       </c>
       <c r="O4" t="n">
-        <v>218.1719903085232</v>
+        <v>217.1719903085232</v>
       </c>
       <c r="P4" t="n">
-        <v>267.2343891315562</v>
+        <v>266.2343891315562</v>
       </c>
       <c r="Q4" t="n">
-        <v>309.383266425598</v>
+        <v>308.383266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>314.0615378172166</v>
+        <v>313.0615378172166</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.99931295557451</v>
+        <v>72.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>41.47457824299391</v>
+        <v>40.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>2.339155739849787</v>
+        <v>1.339155739849787</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -942,25 +942,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>81.71811755106663</v>
+        <v>79.10740598059878</v>
       </c>
       <c r="T5" t="n">
-        <v>177.690094291378</v>
+        <v>176.6900942913779</v>
       </c>
       <c r="U5" t="n">
-        <v>237.3541749278916</v>
+        <v>240.2032864983594</v>
       </c>
       <c r="V5" t="n">
-        <v>221.8510241668239</v>
+        <v>220.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>230.3734759809475</v>
+        <v>229.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>184.2818334606677</v>
+        <v>183.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>103.3174326828064</v>
+        <v>102.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.6190830448386</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>157.703566977272</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>131.7951557829453</v>
+        <v>347</v>
       </c>
       <c r="S6" t="n">
-        <v>56.32664147404526</v>
+        <v>347</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>267.1519411305875</v>
+        <v>257.1223399647953</v>
       </c>
       <c r="W6" t="n">
-        <v>349</v>
+        <v>23.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>349</v>
+        <v>10.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1079,25 +1079,25 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5341199610578595</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>96.80197205828759</v>
+        <v>95.05458694706036</v>
       </c>
       <c r="N7" t="n">
-        <v>147.7318293700456</v>
+        <v>146.7318293700456</v>
       </c>
       <c r="O7" t="n">
-        <v>218.1719903085232</v>
+        <v>217.1719903085232</v>
       </c>
       <c r="P7" t="n">
-        <v>267.2343891315562</v>
+        <v>266.2343891315562</v>
       </c>
       <c r="Q7" t="n">
-        <v>309.383266425598</v>
+        <v>308.383266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>314.0615378172166</v>
+        <v>313.0615378172166</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73.99931295557451</v>
+        <v>72.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>41.47457824299391</v>
+        <v>40.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>2.339155739849787</v>
+        <v>1.339155739849787</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1176,28 +1176,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03168842953230069</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>81.7181175510666</v>
+        <v>79.10740598059878</v>
       </c>
       <c r="T8" t="n">
-        <v>177.6900942913779</v>
+        <v>176.690094291378</v>
       </c>
       <c r="U8" t="n">
-        <v>241.2032864983594</v>
+        <v>240.2032864983594</v>
       </c>
       <c r="V8" t="n">
-        <v>221.8510241668239</v>
+        <v>220.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>230.3734759809475</v>
+        <v>229.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>184.2818334606677</v>
+        <v>183.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>103.3174326828064</v>
+        <v>102.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1216,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>70.89094650296505</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>157.703566977272</v>
       </c>
       <c r="R9" t="n">
-        <v>350</v>
+        <v>130.7951557829453</v>
       </c>
       <c r="S9" t="n">
-        <v>350</v>
+        <v>305.1054396948041</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.510667191520156</v>
+        <v>347</v>
       </c>
       <c r="W9" t="n">
-        <v>24.37314290982852</v>
+        <v>23.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>11.86273944538755</v>
+        <v>347</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,25 +1316,25 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5341199610578542</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>96.80197205828756</v>
+        <v>95.05458694706059</v>
       </c>
       <c r="N10" t="n">
-        <v>147.7318293700456</v>
+        <v>146.7318293700456</v>
       </c>
       <c r="O10" t="n">
-        <v>218.1719903085232</v>
+        <v>217.1719903085232</v>
       </c>
       <c r="P10" t="n">
-        <v>267.2343891315562</v>
+        <v>266.2343891315562</v>
       </c>
       <c r="Q10" t="n">
-        <v>309.383266425598</v>
+        <v>308.383266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>314.0615378172166</v>
+        <v>313.0615378172166</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>46.47457824299391</v>
       </c>
       <c r="D11" t="n">
-        <v>7.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1.363289606868648</v>
@@ -1383,7 +1383,7 @@
         <v>0.5322466588755067</v>
       </c>
       <c r="H11" t="n">
-        <v>2.704090864331428</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>61.3069501425114</v>
+        <v>86.71811755106663</v>
       </c>
       <c r="T11" t="n">
         <v>182.690094291378</v>
@@ -1434,7 +1434,7 @@
         <v>189.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>108.3174326828064</v>
+        <v>89.06871187843238</v>
       </c>
     </row>
     <row r="12">
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="C12" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>189.5954489025972</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>212.9792160800278</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>157.703566977272</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>136.7951557829453</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>11.51066719152016</v>
+        <v>137.7681538890642</v>
       </c>
       <c r="W12" t="n">
         <v>29.37314290982852</v>
@@ -1568,7 +1568,7 @@
         <v>272.2343891315562</v>
       </c>
       <c r="Q13" t="n">
-        <v>314.383266425598</v>
+        <v>310.9097613533131</v>
       </c>
       <c r="R13" t="n">
         <v>319.0615378172166</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>61.3069501425114</v>
+        <v>86.71811755106663</v>
       </c>
       <c r="T14" t="n">
         <v>182.690094291378</v>
       </c>
       <c r="U14" t="n">
-        <v>246.2032864983594</v>
+        <v>216.9113190898042</v>
       </c>
       <c r="V14" t="n">
         <v>226.8510241668239</v>
@@ -1690,19 +1690,19 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.6190830448386</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>212.9792160800278</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>358</v>
+        <v>226.0673197678113</v>
       </c>
       <c r="S15" t="n">
-        <v>322.3792839545347</v>
+        <v>357</v>
       </c>
       <c r="T15" t="n">
         <v>1.872255783551552</v>
       </c>
       <c r="U15" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>11.51066719152016</v>
@@ -1793,7 +1793,7 @@
         <v>5.53411996105786</v>
       </c>
       <c r="M16" t="n">
-        <v>101.8019720582876</v>
+        <v>98.32846698600292</v>
       </c>
       <c r="N16" t="n">
         <v>152.7318293700456</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0.7040908643314281</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3739975652007929</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>84.71811755106663</v>
+        <v>81.91540598059893</v>
       </c>
       <c r="T17" t="n">
         <v>180.690094291378</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>328.2005473667966</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>212.9792160800278</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,16 +1966,16 @@
         <v>157.703566977272</v>
       </c>
       <c r="R18" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="S18" t="n">
         <v>59.32664147404526</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="U18" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>9.510667191520156</v>
@@ -1987,7 +1987,7 @@
         <v>14.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>113.2213312867689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2088,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7040908643314197</v>
+        <v>0.7040908643314281</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,13 +2124,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3739975652008456</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>84.7181175510666</v>
+        <v>81.91540598059893</v>
       </c>
       <c r="T20" t="n">
-        <v>180.6900942913779</v>
+        <v>180.690094291378</v>
       </c>
       <c r="U20" t="n">
         <v>244.2032864983594</v>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>337.4261755038235</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>157.703566977272</v>
       </c>
       <c r="R21" t="n">
-        <v>134.7951557829454</v>
+        <v>134.7951557829453</v>
       </c>
       <c r="S21" t="n">
-        <v>59.32664147404529</v>
+        <v>59.32664147404526</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>358</v>
+        <v>9.510667191520156</v>
       </c>
       <c r="W21" t="n">
         <v>27.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>18.12748491881874</v>
+        <v>14.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3.534119961057854</v>
+        <v>3.53411996105786</v>
       </c>
       <c r="M22" t="n">
-        <v>99.80197205828756</v>
+        <v>99.80197205828759</v>
       </c>
       <c r="N22" t="n">
         <v>150.7318293700456</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3739975652008562</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>233.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>187.2818334606677</v>
+        <v>184.4791218902</v>
       </c>
       <c r="Y23" t="n">
         <v>106.3174326828064</v>
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>42.85363317840771</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>325.6190830448386</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>212.9792160800278</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>157.703566977272</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>358</v>
+        <v>134.7951557829454</v>
       </c>
       <c r="S24" t="n">
-        <v>358</v>
+        <v>59.32664147404529</v>
       </c>
       <c r="T24" t="n">
-        <v>172.5479727608142</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2562,13 +2562,13 @@
         <v>18.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>2.399474803611328</v>
+        <v>18.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>17.53224665887552</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>19.70409086433142</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>103.7181175510666</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>199.6900942913779</v>
       </c>
       <c r="U26" t="n">
-        <v>263.2032864983594</v>
+        <v>64.70223664087089</v>
       </c>
       <c r="V26" t="n">
         <v>243.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>252.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>206.2818334606677</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>243.0342675456871</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>325.6190830448386</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>157.703566977272</v>
       </c>
       <c r="R27" t="n">
         <v>153.7951557829454</v>
@@ -2689,16 +2689,16 @@
         <v>14.20243523188486</v>
       </c>
       <c r="V27" t="n">
-        <v>28.51066719152016</v>
+        <v>348</v>
       </c>
       <c r="W27" t="n">
         <v>46.37314290982852</v>
       </c>
       <c r="X27" t="n">
-        <v>33.86273944538755</v>
+        <v>154.6936313943495</v>
       </c>
       <c r="Y27" t="n">
-        <v>347</v>
+        <v>13.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>118.8019720582876</v>
       </c>
       <c r="N28" t="n">
         <v>169.7318293700456</v>
@@ -2753,10 +2753,10 @@
         <v>289.2343891315562</v>
       </c>
       <c r="Q28" t="n">
-        <v>331.383266425598</v>
+        <v>196.5166813143708</v>
       </c>
       <c r="R28" t="n">
-        <v>316.1161247642769</v>
+        <v>336.0615378172166</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2793,19 +2793,19 @@
         <v>56.47457824299391</v>
       </c>
       <c r="D29" t="n">
-        <v>17.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>11.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>11.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>10.53224665887551</v>
       </c>
       <c r="H29" t="n">
-        <v>12.70409086433143</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>96.71811755106663</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>192.690094291378</v>
+        <v>138.4852093529509</v>
       </c>
       <c r="U29" t="n">
-        <v>48.10331908980408</v>
+        <v>256.2032864983594</v>
       </c>
       <c r="V29" t="n">
         <v>236.8510241668239</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>325.6190830448386</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2926,13 +2926,13 @@
         <v>7.202435231884861</v>
       </c>
       <c r="V30" t="n">
-        <v>188.8231179036293</v>
+        <v>21.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="X30" t="n">
-        <v>26.86273944538755</v>
+        <v>214.5561071126579</v>
       </c>
       <c r="Y30" t="n">
         <v>6.391392766134345</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>15.53411996105786</v>
       </c>
       <c r="M31" t="n">
         <v>111.8019720582876</v>
@@ -2987,13 +2987,13 @@
         <v>233.1719903085232</v>
       </c>
       <c r="P31" t="n">
-        <v>185.4870040203291</v>
+        <v>282.2343891315562</v>
       </c>
       <c r="Q31" t="n">
         <v>324.383266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>329.0615378172166</v>
+        <v>220.6608327449316</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>71.99931295557451</v>
+        <v>72.99931295557451</v>
       </c>
       <c r="C32" t="n">
-        <v>39.47457824299391</v>
+        <v>40.47457824299391</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3391557398497866</v>
+        <v>1.339155739849787</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4.508488429532081</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3072,28 +3072,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.270088429532215</v>
       </c>
       <c r="S32" t="n">
-        <v>79.71811755106663</v>
+        <v>80.71811755106663</v>
       </c>
       <c r="T32" t="n">
-        <v>175.690094291378</v>
+        <v>176.690094291378</v>
       </c>
       <c r="U32" t="n">
-        <v>239.2032864983594</v>
+        <v>240.2032864983594</v>
       </c>
       <c r="V32" t="n">
-        <v>219.8510241668239</v>
+        <v>220.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>228.3734759809475</v>
+        <v>229.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>182.2818334606677</v>
+        <v>183.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>101.3174326828064</v>
+        <v>102.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>157.703566977272</v>
       </c>
       <c r="R33" t="n">
-        <v>129.7951557829453</v>
+        <v>130.7951557829453</v>
       </c>
       <c r="S33" t="n">
-        <v>309.1054396948044</v>
+        <v>55.32664147404526</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3163,13 +3163,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>346</v>
+        <v>236.9160587753713</v>
       </c>
       <c r="W33" t="n">
-        <v>22.37314290982852</v>
+        <v>23.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>346</v>
+        <v>10.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3215,22 +3215,22 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>94.80197205828759</v>
+        <v>95.80197205828759</v>
       </c>
       <c r="N34" t="n">
-        <v>145.7318293700456</v>
+        <v>146.7318293700456</v>
       </c>
       <c r="O34" t="n">
-        <v>216.1719903085232</v>
+        <v>217.1719903085232</v>
       </c>
       <c r="P34" t="n">
-        <v>265.2343891315562</v>
+        <v>266.2343891315562</v>
       </c>
       <c r="Q34" t="n">
-        <v>307.383266425598</v>
+        <v>308.383266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>312.0615378172166</v>
+        <v>313.0615378172166</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0.8012441693821369</v>
       </c>
       <c r="S35" t="n">
-        <v>76.71811755106663</v>
+        <v>76.7181175510666</v>
       </c>
       <c r="T35" t="n">
-        <v>172.690094291378</v>
+        <v>172.6900942913779</v>
       </c>
       <c r="U35" t="n">
         <v>236.2032864983594</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>285.2633645975348</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>297.6412739390635</v>
       </c>
       <c r="H36" t="n">
-        <v>331.0047664317041</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>157.703566977272</v>
       </c>
       <c r="R36" t="n">
-        <v>126.7951557829453</v>
+        <v>126.7951557829454</v>
       </c>
       <c r="S36" t="n">
-        <v>51.32664147404526</v>
+        <v>51.32664147404529</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3403,10 +3403,10 @@
         <v>1.510667191520156</v>
       </c>
       <c r="W36" t="n">
-        <v>19.37314290982852</v>
+        <v>338.0000000000019</v>
       </c>
       <c r="X36" t="n">
-        <v>338</v>
+        <v>338.0000000000019</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>91.80197205828759</v>
+        <v>91.80197205828756</v>
       </c>
       <c r="N37" t="n">
         <v>142.7318293700456</v>
       </c>
       <c r="O37" t="n">
-        <v>213.1719903085232</v>
+        <v>201.4974051972959</v>
       </c>
       <c r="P37" t="n">
         <v>262.2343891315562</v>
@@ -3467,7 +3467,7 @@
         <v>304.383266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>297.3869527059895</v>
+        <v>309.0615378172166</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8012441693820737</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.8012441693821369</v>
       </c>
       <c r="S38" t="n">
         <v>76.71811755106663</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>290.7815421073086</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>325.6190830448386</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>331.0047664317041</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3637,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>338</v>
+        <v>1.510667191520156</v>
       </c>
       <c r="W39" t="n">
         <v>19.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>292.1597151759204</v>
+        <v>6.862739445387547</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>80.12738694706027</v>
+        <v>91.80197205828759</v>
       </c>
       <c r="N40" t="n">
         <v>142.7318293700456</v>
@@ -3704,7 +3704,7 @@
         <v>304.383266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>309.0615378172166</v>
+        <v>297.3869527059895</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3738,22 +3738,22 @@
         <v>168.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>136.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>18.67004710466654</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>91.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>92.70409086433143</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>22.8873207531799</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>316.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>325.3734759809475</v>
@@ -3935,10 +3935,10 @@
         <v>313.1719903085232</v>
       </c>
       <c r="P43" t="n">
-        <v>338</v>
+        <v>338.0000000000164</v>
       </c>
       <c r="Q43" t="n">
-        <v>127.1273105850058</v>
+        <v>127.1273105849894</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>183.7181175510666</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>279.6900942913779</v>
       </c>
       <c r="U44" t="n">
-        <v>338.0000000000011</v>
+        <v>29.99988538104984</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>155.4080972234932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>227.6447801717669</v>
+        <v>233.7951557829453</v>
       </c>
       <c r="S45" t="n">
-        <v>158.3266414740453</v>
+        <v>152.1762658628668</v>
       </c>
       <c r="T45" t="n">
         <v>98.87225578355155</v>
@@ -4166,19 +4166,19 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>249.7318293700456</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>320.1719903085232</v>
+        <v>129.982411431528</v>
       </c>
       <c r="P46" t="n">
-        <v>236.0785917539547</v>
+        <v>338.0000000003224</v>
       </c>
       <c r="Q46" t="n">
-        <v>338</v>
+        <v>338.0000000003535</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>338.0000000003197</v>
       </c>
       <c r="S46" t="n">
         <v>54.61361085039642</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.28830546704647</v>
+        <v>69.99609493216536</v>
       </c>
       <c r="C2" t="n">
-        <v>30.28278357560585</v>
+        <v>29.11268256550484</v>
       </c>
       <c r="D2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="E2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="F2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="G2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="H2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="I2" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="J2" t="n">
-        <v>27.92</v>
+        <v>371.29</v>
       </c>
       <c r="K2" t="n">
-        <v>56.27045587939698</v>
+        <v>399.640455879397</v>
       </c>
       <c r="L2" t="n">
-        <v>91.44170331658292</v>
+        <v>434.8117033165829</v>
       </c>
       <c r="M2" t="n">
-        <v>436.9517033165829</v>
+        <v>434.811703316583</v>
       </c>
       <c r="N2" t="n">
-        <v>782.4617033165829</v>
+        <v>700.9400000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1018.724576173943</v>
+        <v>700.9400000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1050.49</v>
+        <v>1044.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="R2" t="n">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="S2" t="n">
-        <v>1313.456446918115</v>
+        <v>1306.466547928216</v>
       </c>
       <c r="T2" t="n">
-        <v>1133.97150318945</v>
+        <v>1127.991705209652</v>
       </c>
       <c r="U2" t="n">
-        <v>890.3318198577739</v>
+        <v>885.3621228880768</v>
       </c>
       <c r="V2" t="n">
-        <v>666.2398762549215</v>
+        <v>663.9072616796363</v>
       </c>
       <c r="W2" t="n">
-        <v>433.5393954660855</v>
+        <v>432.2168819009014</v>
       </c>
       <c r="X2" t="n">
-        <v>247.3961293441989</v>
+        <v>247.0837167891158</v>
       </c>
       <c r="Y2" t="n">
-        <v>143.0350862302531</v>
+        <v>143.732774685271</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>356.8281646917562</v>
+        <v>1086.260626280672</v>
       </c>
       <c r="C3" t="n">
-        <v>356.8281646917562</v>
+        <v>1086.260626280672</v>
       </c>
       <c r="D3" t="n">
-        <v>356.8281646917562</v>
+        <v>735.7555757756214</v>
       </c>
       <c r="E3" t="n">
-        <v>356.8281646917562</v>
+        <v>735.7555757756214</v>
       </c>
       <c r="F3" t="n">
-        <v>356.8281646917562</v>
+        <v>392.6886643232205</v>
       </c>
       <c r="G3" t="n">
-        <v>27.92</v>
+        <v>63.78049963146429</v>
       </c>
       <c r="H3" t="n">
-        <v>27.92</v>
+        <v>63.78049963146429</v>
       </c>
       <c r="I3" t="n">
-        <v>27.92</v>
+        <v>63.78049963146429</v>
       </c>
       <c r="J3" t="n">
-        <v>163.1428696092612</v>
+        <v>199.0033692407255</v>
       </c>
       <c r="K3" t="n">
-        <v>371.591671364022</v>
+        <v>407.4521709954863</v>
       </c>
       <c r="L3" t="n">
-        <v>668.8341820158259</v>
+        <v>704.6946816472902</v>
       </c>
       <c r="M3" t="n">
-        <v>785.1295237586852</v>
+        <v>820.9900233901494</v>
       </c>
       <c r="N3" t="n">
-        <v>949.4243042153101</v>
+        <v>985.2848038467744</v>
       </c>
       <c r="O3" t="n">
-        <v>1216.838960427331</v>
+        <v>1252.699460058795</v>
       </c>
       <c r="P3" t="n">
-        <v>1352.139500368536</v>
+        <v>1388</v>
       </c>
       <c r="Q3" t="n">
-        <v>1192.842968068261</v>
+        <v>1388</v>
       </c>
       <c r="R3" t="n">
-        <v>1059.716548085488</v>
+        <v>1255.883681027328</v>
       </c>
       <c r="S3" t="n">
-        <v>1002.820950636957</v>
+        <v>1199.998184588898</v>
       </c>
       <c r="T3" t="n">
-        <v>1002.820950636957</v>
+        <v>1126.40865612586</v>
       </c>
       <c r="U3" t="n">
-        <v>1002.820950636957</v>
+        <v>1126.40865612586</v>
       </c>
       <c r="V3" t="n">
-        <v>996.2445191303713</v>
+        <v>1120.842325629375</v>
       </c>
       <c r="W3" t="n">
-        <v>709.3534172170088</v>
+        <v>1097.233090366922</v>
       </c>
       <c r="X3" t="n">
-        <v>356.8281646917562</v>
+        <v>1086.260626280672</v>
       </c>
       <c r="Y3" t="n">
-        <v>356.8281646917562</v>
+        <v>1086.260626280672</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>413.5942345419785</v>
+        <v>657.3908728873029</v>
       </c>
       <c r="C4" t="n">
-        <v>547.5162403604143</v>
+        <v>792.3028787057386</v>
       </c>
       <c r="D4" t="n">
-        <v>668.7553844854143</v>
+        <v>914.5320228307387</v>
       </c>
       <c r="E4" t="n">
-        <v>668.7553844854143</v>
+        <v>1041.270927042152</v>
       </c>
       <c r="F4" t="n">
-        <v>801.0363570773497</v>
+        <v>1174.541899634087</v>
       </c>
       <c r="G4" t="n">
-        <v>801.0363570773497</v>
+        <v>1336.958439291464</v>
       </c>
       <c r="H4" t="n">
-        <v>979.3617999416654</v>
+        <v>1336.958439291464</v>
       </c>
       <c r="I4" t="n">
-        <v>1211.421162812175</v>
+        <v>1336.958439291464</v>
       </c>
       <c r="J4" t="n">
-        <v>1265.615487265472</v>
+        <v>1336.958439291464</v>
       </c>
       <c r="K4" t="n">
-        <v>1395.51505562857</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="L4" t="n">
-        <v>1394.975540516391</v>
+        <v>1388</v>
       </c>
       <c r="M4" t="n">
-        <v>1297.195770760545</v>
+        <v>1291.98526571004</v>
       </c>
       <c r="N4" t="n">
-        <v>1147.971700689792</v>
+        <v>1143.771296649388</v>
       </c>
       <c r="O4" t="n">
-        <v>927.595952903405</v>
+        <v>924.4056498731019</v>
       </c>
       <c r="P4" t="n">
-        <v>657.6622265078936</v>
+        <v>655.4820244876915</v>
       </c>
       <c r="Q4" t="n">
-        <v>345.1538765830471</v>
+        <v>343.9837755729461</v>
       </c>
       <c r="R4" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="S4" t="n">
-        <v>74.83252525810755</v>
+        <v>75.66252525810755</v>
       </c>
       <c r="T4" t="n">
-        <v>74.83252525810755</v>
+        <v>75.66252525810755</v>
       </c>
       <c r="U4" t="n">
-        <v>74.83252525810755</v>
+        <v>75.66252525810755</v>
       </c>
       <c r="V4" t="n">
-        <v>74.83252525810755</v>
+        <v>75.66252525810755</v>
       </c>
       <c r="W4" t="n">
-        <v>254.643443517785</v>
+        <v>256.463443517785</v>
       </c>
       <c r="X4" t="n">
-        <v>413.5942345419785</v>
+        <v>416.4042345419785</v>
       </c>
       <c r="Y4" t="n">
-        <v>413.5942345419785</v>
+        <v>536.7235352210107</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.17629695236738</v>
+        <v>69.99609493216536</v>
       </c>
       <c r="C5" t="n">
-        <v>30.28278357560585</v>
+        <v>29.11268256550484</v>
       </c>
       <c r="D5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="E5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="F5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="G5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="H5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="I5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="J5" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="K5" t="n">
-        <v>56.27045587939698</v>
+        <v>56.11045587939699</v>
       </c>
       <c r="L5" t="n">
-        <v>91.44170331658292</v>
+        <v>325.6445761739431</v>
       </c>
       <c r="M5" t="n">
-        <v>436.9517033165829</v>
+        <v>669.174576173943</v>
       </c>
       <c r="N5" t="n">
-        <v>782.4617033165829</v>
+        <v>1012.704576173943</v>
       </c>
       <c r="O5" t="n">
-        <v>1018.724576173943</v>
+        <v>1012.704576173943</v>
       </c>
       <c r="P5" t="n">
-        <v>1050.49</v>
+        <v>1044.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="R5" t="n">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="S5" t="n">
-        <v>1313.456446918115</v>
+        <v>1308.093529312526</v>
       </c>
       <c r="T5" t="n">
-        <v>1133.97150318945</v>
+        <v>1129.618686593963</v>
       </c>
       <c r="U5" t="n">
-        <v>894.2198113430949</v>
+        <v>886.9891042723877</v>
       </c>
       <c r="V5" t="n">
-        <v>670.1278677402424</v>
+        <v>663.9072616796363</v>
       </c>
       <c r="W5" t="n">
-        <v>437.4273869514064</v>
+        <v>432.2168819009014</v>
       </c>
       <c r="X5" t="n">
-        <v>251.2841208295198</v>
+        <v>247.0837167891158</v>
       </c>
       <c r="Y5" t="n">
-        <v>146.923077715574</v>
+        <v>143.732774685271</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="C6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="D6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="E6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="F6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="G6" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="H6" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="I6" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="J6" t="n">
-        <v>163.1428696092612</v>
+        <v>162.9828696092612</v>
       </c>
       <c r="K6" t="n">
-        <v>371.591671364022</v>
+        <v>371.431671364022</v>
       </c>
       <c r="L6" t="n">
-        <v>668.8341820158259</v>
+        <v>668.6741820158259</v>
       </c>
       <c r="M6" t="n">
-        <v>785.1295237586852</v>
+        <v>784.9695237586851</v>
       </c>
       <c r="N6" t="n">
-        <v>949.4243042153101</v>
+        <v>949.2643042153101</v>
       </c>
       <c r="O6" t="n">
-        <v>1216.838960427331</v>
+        <v>1216.678960427331</v>
       </c>
       <c r="P6" t="n">
-        <v>1352.139500368536</v>
+        <v>1351.979500368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1192.842968068261</v>
+        <v>1351.979500368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1059.716548085488</v>
+        <v>1001.474449863485</v>
       </c>
       <c r="S6" t="n">
-        <v>1002.820950636957</v>
+        <v>650.9693993584344</v>
       </c>
       <c r="T6" t="n">
-        <v>1002.820950636957</v>
+        <v>650.9693993584344</v>
       </c>
       <c r="U6" t="n">
-        <v>1002.820950636957</v>
+        <v>650.9693993584344</v>
       </c>
       <c r="V6" t="n">
-        <v>732.9705050505052</v>
+        <v>391.2498640404593</v>
       </c>
       <c r="W6" t="n">
-        <v>380.4452525252526</v>
+        <v>367.6406287780063</v>
       </c>
       <c r="X6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
       <c r="Y6" t="n">
-        <v>27.92</v>
+        <v>356.6681646917562</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>266.9266383453244</v>
+        <v>148.4273376662921</v>
       </c>
       <c r="C7" t="n">
-        <v>400.8486441637602</v>
+        <v>283.3393434847279</v>
       </c>
       <c r="D7" t="n">
-        <v>522.0877882887603</v>
+        <v>405.568487609728</v>
       </c>
       <c r="E7" t="n">
-        <v>647.8366925001733</v>
+        <v>532.307391821141</v>
       </c>
       <c r="F7" t="n">
-        <v>780.1176650921088</v>
+        <v>665.5783644130764</v>
       </c>
       <c r="G7" t="n">
-        <v>941.544204749486</v>
+        <v>827.9949040704535</v>
       </c>
       <c r="H7" t="n">
-        <v>1119.869647613802</v>
+        <v>1007.310346934769</v>
       </c>
       <c r="I7" t="n">
-        <v>1119.869647613802</v>
+        <v>1240.359709805278</v>
       </c>
       <c r="J7" t="n">
-        <v>1395.515055628571</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="K7" t="n">
-        <v>1395.515055628571</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="L7" t="n">
-        <v>1394.975540516391</v>
+        <v>1388</v>
       </c>
       <c r="M7" t="n">
-        <v>1297.195770760545</v>
+        <v>1291.98526571004</v>
       </c>
       <c r="N7" t="n">
-        <v>1147.971700689792</v>
+        <v>1143.771296649388</v>
       </c>
       <c r="O7" t="n">
-        <v>927.5959529034049</v>
+        <v>924.4056498731019</v>
       </c>
       <c r="P7" t="n">
-        <v>657.6622265078936</v>
+        <v>655.4820244876915</v>
       </c>
       <c r="Q7" t="n">
-        <v>345.1538765830471</v>
+        <v>343.9837755729461</v>
       </c>
       <c r="R7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="S7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="T7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="U7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="V7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="W7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="X7" t="n">
-        <v>27.92</v>
+        <v>27.76</v>
       </c>
       <c r="Y7" t="n">
-        <v>147.2493006790323</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72.25629695236738</v>
+        <v>69.99609493216536</v>
       </c>
       <c r="C8" t="n">
-        <v>30.36278357560585</v>
+        <v>29.11268256550484</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="J8" t="n">
-        <v>374.5</v>
+        <v>27.76</v>
       </c>
       <c r="K8" t="n">
-        <v>402.850455879397</v>
+        <v>290.4733287367571</v>
       </c>
       <c r="L8" t="n">
-        <v>438.0217033165829</v>
+        <v>325.6445761739431</v>
       </c>
       <c r="M8" t="n">
-        <v>784.5217033165829</v>
+        <v>669.174576173943</v>
       </c>
       <c r="N8" t="n">
-        <v>1021.734576173943</v>
+        <v>1012.704576173943</v>
       </c>
       <c r="O8" t="n">
-        <v>1021.734576173943</v>
+        <v>1012.704576173943</v>
       </c>
       <c r="P8" t="n">
-        <v>1053.5</v>
+        <v>1044.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>1400</v>
+        <v>1388</v>
       </c>
       <c r="R8" t="n">
-        <v>1399.967991485321</v>
+        <v>1388</v>
       </c>
       <c r="S8" t="n">
-        <v>1317.424438403435</v>
+        <v>1308.093529312526</v>
       </c>
       <c r="T8" t="n">
-        <v>1137.939494674771</v>
+        <v>1129.618686593963</v>
       </c>
       <c r="U8" t="n">
-        <v>894.2998113430948</v>
+        <v>886.9891042723877</v>
       </c>
       <c r="V8" t="n">
-        <v>670.2078677402424</v>
+        <v>663.9072616796363</v>
       </c>
       <c r="W8" t="n">
-        <v>437.5073869514064</v>
+        <v>432.2168819009014</v>
       </c>
       <c r="X8" t="n">
-        <v>251.3641208295198</v>
+        <v>247.0837167891158</v>
       </c>
       <c r="Y8" t="n">
-        <v>147.003077715574</v>
+        <v>143.732774685271</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>442.6739281220626</v>
+        <v>27.76</v>
       </c>
       <c r="C9" t="n">
-        <v>442.6739281220626</v>
+        <v>27.76</v>
       </c>
       <c r="D9" t="n">
-        <v>442.6739281220626</v>
+        <v>27.76</v>
       </c>
       <c r="E9" t="n">
-        <v>371.0669114524009</v>
+        <v>27.76</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="H9" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="J9" t="n">
-        <v>163.2228696092612</v>
+        <v>162.9828696092612</v>
       </c>
       <c r="K9" t="n">
-        <v>371.671671364022</v>
+        <v>371.431671364022</v>
       </c>
       <c r="L9" t="n">
-        <v>668.9141820158259</v>
+        <v>668.6741820158259</v>
       </c>
       <c r="M9" t="n">
-        <v>785.2095237586851</v>
+        <v>784.9695237586851</v>
       </c>
       <c r="N9" t="n">
-        <v>949.5043042153101</v>
+        <v>949.2643042153101</v>
       </c>
       <c r="O9" t="n">
-        <v>1216.918960427331</v>
+        <v>1216.678960427331</v>
       </c>
       <c r="P9" t="n">
-        <v>1352.219500368536</v>
+        <v>1351.979500368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1192.922968068261</v>
+        <v>1192.682968068261</v>
       </c>
       <c r="R9" t="n">
-        <v>839.3876145329073</v>
+        <v>1060.566649095589</v>
       </c>
       <c r="S9" t="n">
-        <v>485.8522609975537</v>
+        <v>752.3793362725542</v>
       </c>
       <c r="T9" t="n">
-        <v>485.8522609975537</v>
+        <v>752.3793362725542</v>
       </c>
       <c r="U9" t="n">
-        <v>485.8522609975537</v>
+        <v>752.3793362725542</v>
       </c>
       <c r="V9" t="n">
-        <v>479.2758294909677</v>
+        <v>401.8742857675036</v>
       </c>
       <c r="W9" t="n">
-        <v>454.6564932184136</v>
+        <v>378.2650505050505</v>
       </c>
       <c r="X9" t="n">
-        <v>442.6739281220626</v>
+        <v>27.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>442.6739281220626</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>353.1926169613333</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="C10" t="n">
-        <v>353.1926169613333</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="D10" t="n">
-        <v>353.1926169613333</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="E10" t="n">
-        <v>478.9415211727463</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="F10" t="n">
-        <v>611.2224937646818</v>
+        <v>821.6418510454647</v>
       </c>
       <c r="G10" t="n">
-        <v>772.6490334220589</v>
+        <v>975.1739730266224</v>
       </c>
       <c r="H10" t="n">
-        <v>919.195487265473</v>
+        <v>1154.489415890938</v>
       </c>
       <c r="I10" t="n">
-        <v>919.195487265473</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="J10" t="n">
-        <v>1265.695487265473</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="K10" t="n">
-        <v>1395.595055628571</v>
+        <v>1387.538778761447</v>
       </c>
       <c r="L10" t="n">
-        <v>1395.055540516391</v>
+        <v>1388</v>
       </c>
       <c r="M10" t="n">
-        <v>1297.275770760545</v>
+        <v>1291.98526571004</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.051700689792</v>
+        <v>1143.771296649388</v>
       </c>
       <c r="O10" t="n">
-        <v>927.6759529034049</v>
+        <v>924.4056498731018</v>
       </c>
       <c r="P10" t="n">
-        <v>657.7422265078935</v>
+        <v>655.4820244876915</v>
       </c>
       <c r="Q10" t="n">
-        <v>345.2338765830471</v>
+        <v>343.9837755729461</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>27.76</v>
       </c>
       <c r="S10" t="n">
-        <v>74.91252525810755</v>
+        <v>27.76</v>
       </c>
       <c r="T10" t="n">
-        <v>74.91252525810755</v>
+        <v>225.1728398145426</v>
       </c>
       <c r="U10" t="n">
-        <v>74.91252525810755</v>
+        <v>480.6394855675833</v>
       </c>
       <c r="V10" t="n">
-        <v>74.91252525810755</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="W10" t="n">
-        <v>74.91252525810755</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="X10" t="n">
-        <v>233.8633162823011</v>
+        <v>688.3708784535293</v>
       </c>
       <c r="Y10" t="n">
-        <v>353.1926169613333</v>
+        <v>688.3708784535293</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>89.55211093023348</v>
+        <v>79.32741739065649</v>
       </c>
       <c r="C11" t="n">
-        <v>42.6080925029669</v>
+        <v>32.38339896338991</v>
       </c>
       <c r="D11" t="n">
-        <v>35.194803876856</v>
+        <v>32.38339896338991</v>
       </c>
       <c r="E11" t="n">
-        <v>33.81774366789777</v>
+        <v>31.00633875443168</v>
       </c>
       <c r="F11" t="n">
-        <v>31.90902780121913</v>
+        <v>29.09762288775304</v>
       </c>
       <c r="G11" t="n">
-        <v>31.37140491346609</v>
+        <v>28.56</v>
       </c>
       <c r="H11" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="I11" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J11" t="n">
-        <v>383.06</v>
+        <v>381.9900000000002</v>
       </c>
       <c r="K11" t="n">
-        <v>411.410455879397</v>
+        <v>410.3404558793972</v>
       </c>
       <c r="L11" t="n">
-        <v>446.5817033165829</v>
+        <v>445.5117033165831</v>
       </c>
       <c r="M11" t="n">
-        <v>691.3945761739428</v>
+        <v>798.9417033165832</v>
       </c>
       <c r="N11" t="n">
-        <v>1045.814576173943</v>
+        <v>1152.371703316584</v>
       </c>
       <c r="O11" t="n">
-        <v>1045.814576173943</v>
+        <v>1152.371703316584</v>
       </c>
       <c r="P11" t="n">
-        <v>1077.58</v>
+        <v>1184.137127142641</v>
       </c>
       <c r="Q11" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="R11" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="S11" t="n">
-        <v>1370.073787734837</v>
+        <v>1340.405941867609</v>
       </c>
       <c r="T11" t="n">
-        <v>1185.538338955667</v>
+        <v>1155.87049308844</v>
       </c>
       <c r="U11" t="n">
-        <v>936.8481505734861</v>
+        <v>907.1803047062587</v>
       </c>
       <c r="V11" t="n">
-        <v>707.7057019201286</v>
+        <v>678.0378560529011</v>
       </c>
       <c r="W11" t="n">
-        <v>469.9547160807876</v>
+        <v>440.2868702135602</v>
       </c>
       <c r="X11" t="n">
-        <v>278.760944908396</v>
+        <v>249.0930990411685</v>
       </c>
       <c r="Y11" t="n">
-        <v>169.3493967439451</v>
+        <v>159.1247032043681</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>933.218925050808</v>
+        <v>604.296581899018</v>
       </c>
       <c r="C12" t="n">
-        <v>571.6027634346464</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="D12" t="n">
-        <v>220.1505544470679</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="E12" t="n">
-        <v>28.64</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="F12" t="n">
-        <v>28.64</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="G12" t="n">
-        <v>28.64</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="H12" t="n">
-        <v>28.64</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="I12" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J12" t="n">
-        <v>163.8628696092612</v>
+        <v>163.7828696092612</v>
       </c>
       <c r="K12" t="n">
-        <v>372.311671364022</v>
+        <v>372.231671364022</v>
       </c>
       <c r="L12" t="n">
-        <v>669.554182015826</v>
+        <v>669.4741820158258</v>
       </c>
       <c r="M12" t="n">
-        <v>785.8495237586852</v>
+        <v>785.7695237586851</v>
       </c>
       <c r="N12" t="n">
-        <v>950.1443042153102</v>
+        <v>950.06430421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1217.558960427331</v>
+        <v>1217.478960427331</v>
       </c>
       <c r="P12" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1193.562968068261</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1055.386043034983</v>
+        <v>1214.602575335257</v>
       </c>
       <c r="S12" t="n">
-        <v>993.4399405359471</v>
+        <v>1152.656472836222</v>
       </c>
       <c r="T12" t="n">
-        <v>991.5487730778143</v>
+        <v>1150.765305378089</v>
       </c>
       <c r="U12" t="n">
-        <v>991.5487730778143</v>
+        <v>1150.765305378089</v>
       </c>
       <c r="V12" t="n">
-        <v>979.9218365207232</v>
+        <v>1011.605553974994</v>
       </c>
       <c r="W12" t="n">
-        <v>950.2519951976641</v>
+        <v>981.9357126519346</v>
       </c>
       <c r="X12" t="n">
-        <v>933.218925050808</v>
+        <v>964.9026425050786</v>
       </c>
       <c r="Y12" t="n">
-        <v>933.218925050808</v>
+        <v>964.9026425050786</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>721.0872222931609</v>
+        <v>840.3837201095618</v>
       </c>
       <c r="C13" t="n">
-        <v>850.0592281115967</v>
+        <v>840.3837201095618</v>
       </c>
       <c r="D13" t="n">
-        <v>850.0592281115967</v>
+        <v>956.6728642345619</v>
       </c>
       <c r="E13" t="n">
-        <v>850.0592281115967</v>
+        <v>1077.471768445975</v>
       </c>
       <c r="F13" t="n">
-        <v>850.0592281115967</v>
+        <v>1204.80274103791</v>
       </c>
       <c r="G13" t="n">
-        <v>850.0592281115967</v>
+        <v>1204.80274103791</v>
       </c>
       <c r="H13" t="n">
-        <v>850.0592281115967</v>
+        <v>1204.80274103791</v>
       </c>
       <c r="I13" t="n">
-        <v>1077.168590982106</v>
+        <v>1303.050431636902</v>
       </c>
       <c r="J13" t="n">
-        <v>1431.588590982106</v>
+        <v>1303.050431636902</v>
       </c>
       <c r="K13" t="n">
-        <v>1431.588590982106</v>
+        <v>1428</v>
       </c>
       <c r="L13" t="n">
-        <v>1425.998570819421</v>
+        <v>1422.409979837315</v>
       </c>
       <c r="M13" t="n">
-        <v>1323.16829601307</v>
+        <v>1319.579705030964</v>
       </c>
       <c r="N13" t="n">
-        <v>1168.893720891812</v>
+        <v>1165.305129909706</v>
       </c>
       <c r="O13" t="n">
-        <v>943.46746805492</v>
+        <v>939.8788770728141</v>
       </c>
       <c r="P13" t="n">
-        <v>668.4832366089037</v>
+        <v>664.8946456267978</v>
       </c>
       <c r="Q13" t="n">
-        <v>350.9243816335522</v>
+        <v>350.8443816335522</v>
       </c>
       <c r="R13" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="S13" t="n">
-        <v>28.64</v>
+        <v>70.52252525810755</v>
       </c>
       <c r="T13" t="n">
-        <v>28.64</v>
+        <v>261.9953650726501</v>
       </c>
       <c r="U13" t="n">
-        <v>190.4341201233441</v>
+        <v>511.5220108256908</v>
       </c>
       <c r="V13" t="n">
-        <v>392.22551300929</v>
+        <v>511.5220108256908</v>
       </c>
       <c r="W13" t="n">
-        <v>567.0864312689674</v>
+        <v>686.3829290853682</v>
       </c>
       <c r="X13" t="n">
-        <v>721.0872222931609</v>
+        <v>840.3837201095618</v>
       </c>
       <c r="Y13" t="n">
-        <v>721.0872222931609</v>
+        <v>840.3837201095618</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89.55211093023348</v>
+        <v>89.47211093023348</v>
       </c>
       <c r="C14" t="n">
-        <v>42.6080925029669</v>
+        <v>42.5280925029669</v>
       </c>
       <c r="D14" t="n">
-        <v>35.194803876856</v>
+        <v>35.114803876856</v>
       </c>
       <c r="E14" t="n">
-        <v>33.81774366789777</v>
+        <v>33.73774366789777</v>
       </c>
       <c r="F14" t="n">
-        <v>31.90902780121913</v>
+        <v>31.82902780121913</v>
       </c>
       <c r="G14" t="n">
-        <v>31.37140491346609</v>
+        <v>31.29140491346609</v>
       </c>
       <c r="H14" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="I14" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J14" t="n">
-        <v>28.64</v>
+        <v>381.9900000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>383.06</v>
+        <v>410.3404558793972</v>
       </c>
       <c r="L14" t="n">
-        <v>418.231247437186</v>
+        <v>445.5117033165831</v>
       </c>
       <c r="M14" t="n">
-        <v>772.6512474371859</v>
+        <v>798.9417033165832</v>
       </c>
       <c r="N14" t="n">
-        <v>1127.071247437186</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="O14" t="n">
-        <v>1127.071247437186</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="P14" t="n">
-        <v>1158.836671263243</v>
+        <v>1074.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="R14" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="S14" t="n">
-        <v>1370.073787734837</v>
+        <v>1340.405941867609</v>
       </c>
       <c r="T14" t="n">
-        <v>1185.538338955667</v>
+        <v>1155.87049308844</v>
       </c>
       <c r="U14" t="n">
-        <v>936.8481505734861</v>
+        <v>936.7681505734861</v>
       </c>
       <c r="V14" t="n">
-        <v>707.7057019201286</v>
+        <v>707.6257019201286</v>
       </c>
       <c r="W14" t="n">
-        <v>469.9547160807876</v>
+        <v>469.8747160807876</v>
       </c>
       <c r="X14" t="n">
-        <v>278.760944908396</v>
+        <v>278.680944908396</v>
       </c>
       <c r="Y14" t="n">
-        <v>169.3493967439451</v>
+        <v>169.2693967439451</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>243.7705212929574</v>
+        <v>703.6015962290417</v>
       </c>
       <c r="C15" t="n">
-        <v>243.7705212929574</v>
+        <v>703.6015962290417</v>
       </c>
       <c r="D15" t="n">
-        <v>243.7705212929574</v>
+        <v>703.6015962290417</v>
       </c>
       <c r="E15" t="n">
-        <v>243.7705212929574</v>
+        <v>357.4681646917562</v>
       </c>
       <c r="F15" t="n">
-        <v>243.7705212929574</v>
+        <v>357.4681646917562</v>
       </c>
       <c r="G15" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="H15" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="I15" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J15" t="n">
-        <v>163.8628696092612</v>
+        <v>163.7828696092612</v>
       </c>
       <c r="K15" t="n">
-        <v>372.311671364022</v>
+        <v>372.231671364022</v>
       </c>
       <c r="L15" t="n">
-        <v>669.554182015826</v>
+        <v>669.4741820158258</v>
       </c>
       <c r="M15" t="n">
-        <v>785.8495237586852</v>
+        <v>785.7695237586851</v>
       </c>
       <c r="N15" t="n">
-        <v>950.1443042153102</v>
+        <v>950.06430421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1217.558960427331</v>
+        <v>1217.478960427331</v>
       </c>
       <c r="P15" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="R15" t="n">
-        <v>991.243338752374</v>
+        <v>1124.428672320241</v>
       </c>
       <c r="S15" t="n">
-        <v>665.6076983942581</v>
+        <v>763.8226117141808</v>
       </c>
       <c r="T15" t="n">
-        <v>663.7165309361253</v>
+        <v>761.9314442560479</v>
       </c>
       <c r="U15" t="n">
-        <v>302.1003693199637</v>
+        <v>761.9314442560479</v>
       </c>
       <c r="V15" t="n">
-        <v>290.4734327628726</v>
+        <v>750.3045076989569</v>
       </c>
       <c r="W15" t="n">
-        <v>260.8035914398135</v>
+        <v>720.6346663758977</v>
       </c>
       <c r="X15" t="n">
-        <v>243.7705212929574</v>
+        <v>703.6015962290417</v>
       </c>
       <c r="Y15" t="n">
-        <v>243.7705212929574</v>
+        <v>703.6015962290417</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>345.1587305522381</v>
+        <v>1150.72455613121</v>
       </c>
       <c r="C16" t="n">
-        <v>474.1307363706739</v>
+        <v>1150.72455613121</v>
       </c>
       <c r="D16" t="n">
-        <v>590.419880495674</v>
+        <v>1150.72455613121</v>
       </c>
       <c r="E16" t="n">
-        <v>711.218784707087</v>
+        <v>1271.523460342623</v>
       </c>
       <c r="F16" t="n">
-        <v>838.5497572990225</v>
+        <v>1271.523460342623</v>
       </c>
       <c r="G16" t="n">
-        <v>995.0262969563996</v>
+        <v>1428</v>
       </c>
       <c r="H16" t="n">
-        <v>995.0262969563996</v>
+        <v>1428</v>
       </c>
       <c r="I16" t="n">
-        <v>995.0262969563996</v>
+        <v>1428</v>
       </c>
       <c r="J16" t="n">
-        <v>1306.639022619008</v>
+        <v>1428</v>
       </c>
       <c r="K16" t="n">
-        <v>1431.588590982106</v>
+        <v>1428</v>
       </c>
       <c r="L16" t="n">
-        <v>1425.998570819421</v>
+        <v>1422.409979837315</v>
       </c>
       <c r="M16" t="n">
-        <v>1323.16829601307</v>
+        <v>1323.08829601307</v>
       </c>
       <c r="N16" t="n">
-        <v>1168.893720891812</v>
+        <v>1168.813720891812</v>
       </c>
       <c r="O16" t="n">
-        <v>943.46746805492</v>
+        <v>943.38746805492</v>
       </c>
       <c r="P16" t="n">
-        <v>668.4832366089037</v>
+        <v>668.4032366089036</v>
       </c>
       <c r="Q16" t="n">
-        <v>350.9243816335522</v>
+        <v>350.8443816335522</v>
       </c>
       <c r="R16" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="S16" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="T16" t="n">
-        <v>28.64</v>
+        <v>141.438169863028</v>
       </c>
       <c r="U16" t="n">
-        <v>28.64</v>
+        <v>390.9648156160687</v>
       </c>
       <c r="V16" t="n">
-        <v>230.431392885946</v>
+        <v>592.7562085020146</v>
       </c>
       <c r="W16" t="n">
-        <v>230.431392885946</v>
+        <v>767.617126761692</v>
       </c>
       <c r="X16" t="n">
-        <v>230.431392885946</v>
+        <v>921.6179177858855</v>
       </c>
       <c r="Y16" t="n">
-        <v>230.431392885946</v>
+        <v>1035.997218464918</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80.04588122462221</v>
+        <v>78.87690301297344</v>
       </c>
       <c r="C17" t="n">
-        <v>35.12206481755764</v>
+        <v>33.95308660590888</v>
       </c>
       <c r="D17" t="n">
-        <v>29.72897821164877</v>
+        <v>28.56</v>
       </c>
       <c r="E17" t="n">
-        <v>29.72897821164877</v>
+        <v>29.19034328920004</v>
       </c>
       <c r="F17" t="n">
-        <v>29.72897821164871</v>
+        <v>29.19034328920004</v>
       </c>
       <c r="G17" t="n">
-        <v>29.72897821164871</v>
+        <v>29.27120289326407</v>
       </c>
       <c r="H17" t="n">
-        <v>29.01777531838464</v>
+        <v>28.56</v>
       </c>
       <c r="I17" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J17" t="n">
-        <v>383.06</v>
+        <v>381.9900000000002</v>
       </c>
       <c r="K17" t="n">
-        <v>737.48</v>
+        <v>410.3404558793972</v>
       </c>
       <c r="L17" t="n">
-        <v>772.6512474371859</v>
+        <v>445.5117033165831</v>
       </c>
       <c r="M17" t="n">
-        <v>1045.814576173943</v>
+        <v>798.9417033165832</v>
       </c>
       <c r="N17" t="n">
-        <v>1400.234576173943</v>
+        <v>798.9417033165832</v>
       </c>
       <c r="O17" t="n">
-        <v>1400.234576173943</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="P17" t="n">
-        <v>1432</v>
+        <v>1074.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="R17" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="S17" t="n">
-        <v>1346.426143887812</v>
+        <v>1345.257165676163</v>
       </c>
       <c r="T17" t="n">
-        <v>1163.910897128844</v>
+        <v>1162.741918917195</v>
       </c>
       <c r="U17" t="n">
-        <v>917.2409107668648</v>
+        <v>916.071932555216</v>
       </c>
       <c r="V17" t="n">
-        <v>690.1186641337093</v>
+        <v>688.9496859220606</v>
       </c>
       <c r="W17" t="n">
-        <v>454.3878803145703</v>
+        <v>453.2189021029216</v>
       </c>
       <c r="X17" t="n">
-        <v>265.2143111623807</v>
+        <v>264.0453329507319</v>
       </c>
       <c r="Y17" t="n">
-        <v>157.8229650181318</v>
+        <v>156.653986806483</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="C18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="D18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="E18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="F18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="G18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="H18" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="I18" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J18" t="n">
-        <v>163.8628696092612</v>
+        <v>163.7828696092612</v>
       </c>
       <c r="K18" t="n">
-        <v>372.311671364022</v>
+        <v>372.231671364022</v>
       </c>
       <c r="L18" t="n">
-        <v>669.554182015826</v>
+        <v>669.4741820158258</v>
       </c>
       <c r="M18" t="n">
-        <v>785.8495237586852</v>
+        <v>785.7695237586851</v>
       </c>
       <c r="N18" t="n">
-        <v>950.1443042153102</v>
+        <v>950.06430421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1217.558960427331</v>
+        <v>1217.478960427331</v>
       </c>
       <c r="P18" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1193.562968068261</v>
+        <v>1193.482968068261</v>
       </c>
       <c r="R18" t="n">
-        <v>831.9468064520993</v>
+        <v>832.8769074622002</v>
       </c>
       <c r="S18" t="n">
-        <v>772.0209059732657</v>
+        <v>772.9510069833666</v>
       </c>
       <c r="T18" t="n">
-        <v>772.0209059732657</v>
+        <v>412.344946377306</v>
       </c>
       <c r="U18" t="n">
-        <v>410.4047443571041</v>
+        <v>412.344946377306</v>
       </c>
       <c r="V18" t="n">
-        <v>400.798009820215</v>
+        <v>402.7382118404169</v>
       </c>
       <c r="W18" t="n">
-        <v>373.1483705173579</v>
+        <v>375.0885725375598</v>
       </c>
       <c r="X18" t="n">
-        <v>358.1355023907038</v>
+        <v>360.0757044109057</v>
       </c>
       <c r="Y18" t="n">
-        <v>243.7705212929574</v>
+        <v>360.0757044109057</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1110.360833081155</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="C19" t="n">
-        <v>1165.357300037344</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="D19" t="n">
-        <v>1165.357300037344</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="E19" t="n">
-        <v>1288.136204248756</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="F19" t="n">
-        <v>1417.447176840692</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="G19" t="n">
-        <v>1417.447176840692</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="H19" t="n">
-        <v>1417.447176840692</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="I19" t="n">
-        <v>1417.447176840692</v>
+        <v>1283.144475866017</v>
       </c>
       <c r="J19" t="n">
-        <v>1417.447176840692</v>
+        <v>1417.367176840692</v>
       </c>
       <c r="K19" t="n">
-        <v>1417.447176840692</v>
+        <v>1417.367176840692</v>
       </c>
       <c r="L19" t="n">
-        <v>1413.877358698209</v>
+        <v>1413.797358698209</v>
       </c>
       <c r="M19" t="n">
-        <v>1313.06728591206</v>
+        <v>1312.98728591206</v>
       </c>
       <c r="N19" t="n">
-        <v>1160.812912811004</v>
+        <v>1160.732912811004</v>
       </c>
       <c r="O19" t="n">
-        <v>937.4068619943139</v>
+        <v>937.326861994314</v>
       </c>
       <c r="P19" t="n">
-        <v>664.4428325684996</v>
+        <v>664.3628325684997</v>
       </c>
       <c r="Q19" t="n">
-        <v>348.9041796133502</v>
+        <v>348.8241796133502</v>
       </c>
       <c r="R19" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="S19" t="n">
-        <v>72.58252525810755</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="T19" t="n">
-        <v>266.0353650726501</v>
+        <v>265.9553650726501</v>
       </c>
       <c r="U19" t="n">
-        <v>517.5420108256908</v>
+        <v>517.4620108256909</v>
       </c>
       <c r="V19" t="n">
-        <v>721.3134037116367</v>
+        <v>721.2334037116368</v>
       </c>
       <c r="W19" t="n">
-        <v>721.3134037116367</v>
+        <v>898.0743219713142</v>
       </c>
       <c r="X19" t="n">
-        <v>877.2941947358303</v>
+        <v>1054.055112995508</v>
       </c>
       <c r="Y19" t="n">
-        <v>993.6534954148625</v>
+        <v>1054.055112995508</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79.66810590623756</v>
+        <v>78.87690301297344</v>
       </c>
       <c r="C20" t="n">
-        <v>34.74428949917299</v>
+        <v>33.95308660590888</v>
       </c>
       <c r="D20" t="n">
-        <v>29.35120289326412</v>
+        <v>28.56</v>
       </c>
       <c r="E20" t="n">
-        <v>29.35120289326412</v>
+        <v>29.19034328920004</v>
       </c>
       <c r="F20" t="n">
-        <v>29.35120289326406</v>
+        <v>29.19034328920004</v>
       </c>
       <c r="G20" t="n">
-        <v>29.35120289326406</v>
+        <v>29.27120289326407</v>
       </c>
       <c r="H20" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="I20" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J20" t="n">
-        <v>28.64</v>
+        <v>307.5941202945455</v>
       </c>
       <c r="K20" t="n">
-        <v>383.06</v>
+        <v>335.9445761739425</v>
       </c>
       <c r="L20" t="n">
-        <v>418.231247437186</v>
+        <v>689.3745761739425</v>
       </c>
       <c r="M20" t="n">
-        <v>772.6512474371859</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="N20" t="n">
-        <v>1127.071247437186</v>
+        <v>1396.234576173943</v>
       </c>
       <c r="O20" t="n">
-        <v>1127.071247437186</v>
+        <v>1396.234576173943</v>
       </c>
       <c r="P20" t="n">
-        <v>1158.836671263243</v>
+        <v>1428</v>
       </c>
       <c r="Q20" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="R20" t="n">
-        <v>1431.622224681615</v>
+        <v>1428</v>
       </c>
       <c r="S20" t="n">
-        <v>1346.048368569427</v>
+        <v>1345.257165676163</v>
       </c>
       <c r="T20" t="n">
-        <v>1163.533121810459</v>
+        <v>1162.741918917195</v>
       </c>
       <c r="U20" t="n">
-        <v>916.8631354484801</v>
+        <v>916.071932555216</v>
       </c>
       <c r="V20" t="n">
-        <v>689.7408888153246</v>
+        <v>688.9496859220606</v>
       </c>
       <c r="W20" t="n">
-        <v>454.0101049961856</v>
+        <v>453.2189021029216</v>
       </c>
       <c r="X20" t="n">
-        <v>264.836535843996</v>
+        <v>264.0453329507319</v>
       </c>
       <c r="Y20" t="n">
-        <v>157.4451896997472</v>
+        <v>156.653986806483</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>589.9039528302428</v>
+        <v>584.5250420038901</v>
       </c>
       <c r="C21" t="n">
-        <v>589.9039528302428</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="D21" t="n">
-        <v>589.9039528302428</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="E21" t="n">
-        <v>243.7705212929574</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="F21" t="n">
-        <v>243.7705212929574</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="G21" t="n">
-        <v>243.7705212929574</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="H21" t="n">
-        <v>243.7705212929574</v>
+        <v>243.6905212929574</v>
       </c>
       <c r="I21" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J21" t="n">
-        <v>163.8628696092612</v>
+        <v>163.7828696092612</v>
       </c>
       <c r="K21" t="n">
-        <v>372.311671364022</v>
+        <v>372.231671364022</v>
       </c>
       <c r="L21" t="n">
-        <v>669.554182015826</v>
+        <v>669.4741820158258</v>
       </c>
       <c r="M21" t="n">
-        <v>785.8495237586852</v>
+        <v>785.7695237586851</v>
       </c>
       <c r="N21" t="n">
-        <v>950.1443042153102</v>
+        <v>950.06430421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1217.558960427331</v>
+        <v>1217.478960427331</v>
       </c>
       <c r="P21" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1193.562968068261</v>
+        <v>1193.482968068261</v>
       </c>
       <c r="R21" t="n">
-        <v>1057.406245055185</v>
+        <v>1057.326245055185</v>
       </c>
       <c r="S21" t="n">
-        <v>997.4803445763512</v>
+        <v>997.4003445763511</v>
       </c>
       <c r="T21" t="n">
-        <v>997.4803445763512</v>
+        <v>997.4003445763511</v>
       </c>
       <c r="U21" t="n">
-        <v>997.4803445763512</v>
+        <v>997.4003445763511</v>
       </c>
       <c r="V21" t="n">
-        <v>635.8641829601895</v>
+        <v>987.7936100394621</v>
       </c>
       <c r="W21" t="n">
-        <v>608.2145436573325</v>
+        <v>960.1439707366051</v>
       </c>
       <c r="X21" t="n">
-        <v>589.9039528302428</v>
+        <v>945.131102609951</v>
       </c>
       <c r="Y21" t="n">
-        <v>589.9039528302428</v>
+        <v>945.131102609951</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="C22" t="n">
-        <v>402.3418301508339</v>
+        <v>203.4545310765433</v>
       </c>
       <c r="D22" t="n">
-        <v>402.3418301508339</v>
+        <v>321.7236752015434</v>
       </c>
       <c r="E22" t="n">
-        <v>402.3418301508339</v>
+        <v>444.5025794129564</v>
       </c>
       <c r="F22" t="n">
-        <v>531.6528027427694</v>
+        <v>573.8135520048919</v>
       </c>
       <c r="G22" t="n">
-        <v>531.6528027427694</v>
+        <v>732.270091662269</v>
       </c>
       <c r="H22" t="n">
-        <v>707.008245607085</v>
+        <v>907.6255345265846</v>
       </c>
       <c r="I22" t="n">
-        <v>936.0976084775941</v>
+        <v>937.0076084775941</v>
       </c>
       <c r="J22" t="n">
-        <v>1290.517608477594</v>
+        <v>1290.437608477594</v>
       </c>
       <c r="K22" t="n">
-        <v>1417.447176840692</v>
+        <v>1417.367176840692</v>
       </c>
       <c r="L22" t="n">
-        <v>1413.877358698209</v>
+        <v>1413.797358698209</v>
       </c>
       <c r="M22" t="n">
-        <v>1313.06728591206</v>
+        <v>1312.98728591206</v>
       </c>
       <c r="N22" t="n">
-        <v>1160.812912811004</v>
+        <v>1160.732912811004</v>
       </c>
       <c r="O22" t="n">
-        <v>937.406861994314</v>
+        <v>937.326861994314</v>
       </c>
       <c r="P22" t="n">
-        <v>664.4428325684996</v>
+        <v>664.3628325684997</v>
       </c>
       <c r="Q22" t="n">
-        <v>348.9041796133502</v>
+        <v>348.8241796133502</v>
       </c>
       <c r="R22" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="S22" t="n">
-        <v>72.58252525810755</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="T22" t="n">
-        <v>150.8351843977931</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="U22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="V22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="W22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="X22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
       <c r="Y22" t="n">
-        <v>402.3418301508339</v>
+        <v>72.50252525810754</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80.04588122462221</v>
+        <v>78.87690301297344</v>
       </c>
       <c r="C23" t="n">
-        <v>35.12206481755764</v>
+        <v>33.95308660590888</v>
       </c>
       <c r="D23" t="n">
-        <v>29.72897821164877</v>
+        <v>28.56</v>
       </c>
       <c r="E23" t="n">
-        <v>29.72897821164877</v>
+        <v>28.56</v>
       </c>
       <c r="F23" t="n">
-        <v>29.35120289326406</v>
+        <v>28.56</v>
       </c>
       <c r="G23" t="n">
-        <v>29.35120289326406</v>
+        <v>29.27120289326406</v>
       </c>
       <c r="H23" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="I23" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J23" t="n">
-        <v>383.06</v>
+        <v>381.9900000000002</v>
       </c>
       <c r="K23" t="n">
-        <v>411.410455879397</v>
+        <v>410.3404558793972</v>
       </c>
       <c r="L23" t="n">
-        <v>446.5817033165829</v>
+        <v>445.5117033165831</v>
       </c>
       <c r="M23" t="n">
-        <v>691.3945761739428</v>
+        <v>798.9417033165832</v>
       </c>
       <c r="N23" t="n">
-        <v>1045.814576173943</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="O23" t="n">
-        <v>1045.814576173943</v>
+        <v>1042.804576173943</v>
       </c>
       <c r="P23" t="n">
-        <v>1077.58</v>
+        <v>1074.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="R23" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="S23" t="n">
-        <v>1346.426143887812</v>
+        <v>1342.426143887812</v>
       </c>
       <c r="T23" t="n">
-        <v>1163.910897128844</v>
+        <v>1159.910897128844</v>
       </c>
       <c r="U23" t="n">
-        <v>917.2409107668648</v>
+        <v>913.2409107668648</v>
       </c>
       <c r="V23" t="n">
-        <v>690.1186641337093</v>
+        <v>686.1186641337093</v>
       </c>
       <c r="W23" t="n">
-        <v>454.3878803145703</v>
+        <v>450.3878803145703</v>
       </c>
       <c r="X23" t="n">
-        <v>265.2143111623807</v>
+        <v>264.0453329507319</v>
       </c>
       <c r="Y23" t="n">
-        <v>157.8229650181318</v>
+        <v>156.653986806483</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>243.7705212929574</v>
+        <v>743.8215743041649</v>
       </c>
       <c r="C24" t="n">
-        <v>243.7705212929574</v>
+        <v>743.8215743041649</v>
       </c>
       <c r="D24" t="n">
-        <v>243.7705212929574</v>
+        <v>700.5350761441571</v>
       </c>
       <c r="E24" t="n">
-        <v>243.7705212929574</v>
+        <v>700.5350761441571</v>
       </c>
       <c r="F24" t="n">
-        <v>243.7705212929574</v>
+        <v>357.4681646917562</v>
       </c>
       <c r="G24" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="H24" t="n">
-        <v>243.7705212929574</v>
+        <v>28.56</v>
       </c>
       <c r="I24" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="J24" t="n">
-        <v>163.8628696092612</v>
+        <v>163.7828696092612</v>
       </c>
       <c r="K24" t="n">
-        <v>372.311671364022</v>
+        <v>372.231671364022</v>
       </c>
       <c r="L24" t="n">
-        <v>669.554182015826</v>
+        <v>669.4741820158258</v>
       </c>
       <c r="M24" t="n">
-        <v>785.8495237586852</v>
+        <v>785.7695237586851</v>
       </c>
       <c r="N24" t="n">
-        <v>950.1443042153102</v>
+        <v>950.06430421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1217.558960427331</v>
+        <v>1217.478960427331</v>
       </c>
       <c r="P24" t="n">
-        <v>1352.859500368536</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1193.562968068261</v>
+        <v>1352.779500368536</v>
       </c>
       <c r="R24" t="n">
-        <v>831.9468064520993</v>
+        <v>1216.622777355459</v>
       </c>
       <c r="S24" t="n">
-        <v>470.3306448359376</v>
+        <v>1156.696876876626</v>
       </c>
       <c r="T24" t="n">
-        <v>296.0397632593576</v>
+        <v>1156.696876876626</v>
       </c>
       <c r="U24" t="n">
-        <v>296.0397632593576</v>
+        <v>1156.696876876626</v>
       </c>
       <c r="V24" t="n">
-        <v>286.4330287224686</v>
+        <v>1147.090142339737</v>
       </c>
       <c r="W24" t="n">
-        <v>258.7833894196115</v>
+        <v>1119.44050303688</v>
       </c>
       <c r="X24" t="n">
-        <v>243.7705212929574</v>
+        <v>1104.427634910226</v>
       </c>
       <c r="Y24" t="n">
-        <v>243.7705212929574</v>
+        <v>1104.427634910226</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>361.461709283871</v>
+        <v>1001.029063001781</v>
       </c>
       <c r="C25" t="n">
-        <v>361.461709283871</v>
+        <v>1131.981068820217</v>
       </c>
       <c r="D25" t="n">
-        <v>479.730853408871</v>
+        <v>1131.981068820217</v>
       </c>
       <c r="E25" t="n">
-        <v>479.730853408871</v>
+        <v>1131.981068820217</v>
       </c>
       <c r="F25" t="n">
-        <v>609.0418260008065</v>
+        <v>1131.981068820217</v>
       </c>
       <c r="G25" t="n">
-        <v>767.4983656581836</v>
+        <v>1290.437608477594</v>
       </c>
       <c r="H25" t="n">
-        <v>767.4983656581836</v>
+        <v>1290.437608477594</v>
       </c>
       <c r="I25" t="n">
-        <v>996.5877285286928</v>
+        <v>1290.437608477594</v>
       </c>
       <c r="J25" t="n">
-        <v>1290.517608477594</v>
+        <v>1290.437608477594</v>
       </c>
       <c r="K25" t="n">
-        <v>1417.447176840692</v>
+        <v>1417.367176840692</v>
       </c>
       <c r="L25" t="n">
-        <v>1413.877358698209</v>
+        <v>1413.797358698209</v>
       </c>
       <c r="M25" t="n">
-        <v>1313.06728591206</v>
+        <v>1312.98728591206</v>
       </c>
       <c r="N25" t="n">
-        <v>1160.812912811004</v>
+        <v>1160.732912811004</v>
       </c>
       <c r="O25" t="n">
-        <v>937.406861994314</v>
+        <v>937.3268619943141</v>
       </c>
       <c r="P25" t="n">
-        <v>664.4428325684996</v>
+        <v>664.3628325684997</v>
       </c>
       <c r="Q25" t="n">
-        <v>348.9041796133502</v>
+        <v>348.8241796133502</v>
       </c>
       <c r="R25" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="S25" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="T25" t="n">
-        <v>28.64</v>
+        <v>28.56</v>
       </c>
       <c r="U25" t="n">
-        <v>28.64</v>
+        <v>231.3693224866401</v>
       </c>
       <c r="V25" t="n">
-        <v>28.64</v>
+        <v>435.1407153725861</v>
       </c>
       <c r="W25" t="n">
-        <v>205.4809182596774</v>
+        <v>611.9816336322635</v>
       </c>
       <c r="X25" t="n">
-        <v>361.461709283871</v>
+        <v>767.9624246564571</v>
       </c>
       <c r="Y25" t="n">
-        <v>361.461709283871</v>
+        <v>884.3217253354893</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>137.433230700327</v>
+        <v>191.7824139605365</v>
       </c>
       <c r="C26" t="n">
-        <v>73.3174951013432</v>
+        <v>127.6666783615528</v>
       </c>
       <c r="D26" t="n">
-        <v>48.73248930351513</v>
+        <v>103.0816725637247</v>
       </c>
       <c r="E26" t="n">
-        <v>30.18371192283973</v>
+        <v>84.53289518304929</v>
       </c>
       <c r="F26" t="n">
-        <v>27.76</v>
+        <v>65.45246214465348</v>
       </c>
       <c r="G26" t="n">
-        <v>27.76</v>
+        <v>47.74312208518325</v>
       </c>
       <c r="H26" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="I26" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="J26" t="n">
-        <v>371.29</v>
+        <v>372.36</v>
       </c>
       <c r="K26" t="n">
-        <v>399.640455879397</v>
+        <v>400.710455879397</v>
       </c>
       <c r="L26" t="n">
-        <v>434.8117033165829</v>
+        <v>435.881703316583</v>
       </c>
       <c r="M26" t="n">
-        <v>669.174576173943</v>
+        <v>671.194576173943</v>
       </c>
       <c r="N26" t="n">
-        <v>1012.704576173943</v>
+        <v>1015.714576173943</v>
       </c>
       <c r="O26" t="n">
-        <v>1012.704576173943</v>
+        <v>1015.714576173943</v>
       </c>
       <c r="P26" t="n">
-        <v>1044.47</v>
+        <v>1047.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="R26" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="S26" t="n">
-        <v>1283.234224695892</v>
+        <v>1392</v>
       </c>
       <c r="T26" t="n">
-        <v>1081.527058745006</v>
+        <v>1190.292834049113</v>
       </c>
       <c r="U26" t="n">
-        <v>815.6651531911073</v>
+        <v>1124.937039462375</v>
       </c>
       <c r="V26" t="n">
-        <v>569.3509873660327</v>
+        <v>878.6228736373004</v>
       </c>
       <c r="W26" t="n">
-        <v>569.3509873660327</v>
+        <v>623.7001706262422</v>
       </c>
       <c r="X26" t="n">
-        <v>360.9854990219238</v>
+        <v>415.3346822821334</v>
       </c>
       <c r="Y26" t="n">
-        <v>234.4022336857558</v>
+        <v>288.7514169459653</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>378.2650505050505</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="C27" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="D27" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="E27" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="F27" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="G27" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="H27" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="I27" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="J27" t="n">
-        <v>162.9828696092612</v>
+        <v>163.0628696092612</v>
       </c>
       <c r="K27" t="n">
-        <v>371.431671364022</v>
+        <v>371.5116713640219</v>
       </c>
       <c r="L27" t="n">
-        <v>668.6741820158259</v>
+        <v>668.7541820158258</v>
       </c>
       <c r="M27" t="n">
-        <v>784.9695237586851</v>
+        <v>785.049523758685</v>
       </c>
       <c r="N27" t="n">
-        <v>949.2643042153101</v>
+        <v>949.34430421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1216.678960427331</v>
+        <v>1216.758960427331</v>
       </c>
       <c r="P27" t="n">
-        <v>1351.979500368536</v>
+        <v>1352.059500368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1351.979500368536</v>
+        <v>1192.762968068261</v>
       </c>
       <c r="R27" t="n">
-        <v>1196.63085816354</v>
+        <v>1037.414325863266</v>
       </c>
       <c r="S27" t="n">
-        <v>1117.513038492787</v>
+        <v>958.2965061925127</v>
       </c>
       <c r="T27" t="n">
-        <v>1098.450153862937</v>
+        <v>939.2336215626626</v>
       </c>
       <c r="U27" t="n">
-        <v>1084.104259689316</v>
+        <v>924.8877273890415</v>
       </c>
       <c r="V27" t="n">
-        <v>1055.305605960508</v>
+        <v>573.3725758738899</v>
       </c>
       <c r="W27" t="n">
-        <v>1008.464047465732</v>
+        <v>526.5310173791136</v>
       </c>
       <c r="X27" t="n">
-        <v>974.2592601471587</v>
+        <v>370.2748240514878</v>
       </c>
       <c r="Y27" t="n">
-        <v>623.7542096421082</v>
+        <v>356.7481646917562</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>878.0125803296838</v>
+        <v>705.4544759586414</v>
       </c>
       <c r="C28" t="n">
-        <v>990.1545861481196</v>
+        <v>817.5964817770772</v>
       </c>
       <c r="D28" t="n">
-        <v>1089.61373027312</v>
+        <v>917.0556259020773</v>
       </c>
       <c r="E28" t="n">
-        <v>1089.61373027312</v>
+        <v>917.0556259020773</v>
       </c>
       <c r="F28" t="n">
-        <v>1089.61373027312</v>
+        <v>917.0556259020773</v>
       </c>
       <c r="G28" t="n">
-        <v>1089.61373027312</v>
+        <v>917.0556259020773</v>
       </c>
       <c r="H28" t="n">
-        <v>1246.159173137435</v>
+        <v>1073.601068766393</v>
       </c>
       <c r="I28" t="n">
-        <v>1246.159173137435</v>
+        <v>1283.880431636902</v>
       </c>
       <c r="J28" t="n">
-        <v>1279.880431636902</v>
+        <v>1283.880431636902</v>
       </c>
       <c r="K28" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="L28" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="M28" t="n">
-        <v>1388</v>
+        <v>1271.998008021932</v>
       </c>
       <c r="N28" t="n">
-        <v>1216.553707707025</v>
+        <v>1100.551715728956</v>
       </c>
       <c r="O28" t="n">
-        <v>973.9557376984153</v>
+        <v>857.9537457203471</v>
       </c>
       <c r="P28" t="n">
-        <v>681.7997890806818</v>
+        <v>565.7977971026136</v>
       </c>
       <c r="Q28" t="n">
-        <v>347.0692169336131</v>
+        <v>367.2960988052693</v>
       </c>
       <c r="R28" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="S28" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="T28" t="n">
-        <v>202.4028398145425</v>
+        <v>202.4828398145426</v>
       </c>
       <c r="U28" t="n">
-        <v>202.4028398145425</v>
+        <v>214.806128329446</v>
       </c>
       <c r="V28" t="n">
-        <v>387.3642327004885</v>
+        <v>214.806128329446</v>
       </c>
       <c r="W28" t="n">
-        <v>545.3951509601659</v>
+        <v>372.8370465891234</v>
       </c>
       <c r="X28" t="n">
-        <v>682.5659419843594</v>
+        <v>510.007837613317</v>
       </c>
       <c r="Y28" t="n">
-        <v>780.1152426633917</v>
+        <v>607.5571382923492</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>149.2781715362941</v>
+        <v>95.52366151703981</v>
       </c>
       <c r="C29" t="n">
-        <v>92.23314300801742</v>
+        <v>38.47863298876314</v>
       </c>
       <c r="D29" t="n">
-        <v>74.71884428089642</v>
+        <v>38.47863298876314</v>
       </c>
       <c r="E29" t="n">
-        <v>63.24077397092808</v>
+        <v>38.47863298876314</v>
       </c>
       <c r="F29" t="n">
-        <v>51.23104800323934</v>
+        <v>38.47863298876314</v>
       </c>
       <c r="G29" t="n">
-        <v>40.5924150144762</v>
+        <v>27.84</v>
       </c>
       <c r="H29" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="I29" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="J29" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="K29" t="n">
-        <v>371.29</v>
+        <v>291.5033287367571</v>
       </c>
       <c r="L29" t="n">
-        <v>406.4612474371859</v>
+        <v>326.674576173943</v>
       </c>
       <c r="M29" t="n">
-        <v>749.991247437186</v>
+        <v>671.194576173943</v>
       </c>
       <c r="N29" t="n">
-        <v>1012.704576173943</v>
+        <v>1015.714576173943</v>
       </c>
       <c r="O29" t="n">
-        <v>1012.704576173943</v>
+        <v>1015.714576173943</v>
       </c>
       <c r="P29" t="n">
-        <v>1044.47</v>
+        <v>1047.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="R29" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="S29" t="n">
-        <v>1290.304931766599</v>
+        <v>1392</v>
       </c>
       <c r="T29" t="n">
-        <v>1095.66847288642</v>
+        <v>1252.115950148534</v>
       </c>
       <c r="U29" t="n">
-        <v>1047.079261684597</v>
+        <v>993.324751665343</v>
       </c>
       <c r="V29" t="n">
-        <v>807.8358029302296</v>
+        <v>754.0812929109754</v>
       </c>
       <c r="W29" t="n">
-        <v>559.9838069898786</v>
+        <v>506.2292969706243</v>
       </c>
       <c r="X29" t="n">
-        <v>358.6890257164769</v>
+        <v>304.9345156972225</v>
       </c>
       <c r="Y29" t="n">
-        <v>239.1764674510158</v>
+        <v>185.4219574317615</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>378.2650505050505</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="C30" t="n">
-        <v>378.2650505050505</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="D30" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="E30" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="F30" t="n">
-        <v>27.76</v>
+        <v>356.7481646917562</v>
       </c>
       <c r="G30" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="H30" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="I30" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="J30" t="n">
-        <v>162.9828696092612</v>
+        <v>163.0628696092612</v>
       </c>
       <c r="K30" t="n">
-        <v>371.431671364022</v>
+        <v>371.5116713640219</v>
       </c>
       <c r="L30" t="n">
-        <v>668.6741820158259</v>
+        <v>668.7541820158258</v>
       </c>
       <c r="M30" t="n">
-        <v>784.9695237586851</v>
+        <v>785.049523758685</v>
       </c>
       <c r="N30" t="n">
-        <v>949.2643042153101</v>
+        <v>949.34430421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1216.678960427331</v>
+        <v>1216.758960427331</v>
       </c>
       <c r="P30" t="n">
-        <v>1351.979500368536</v>
+        <v>1352.059500368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1192.682968068261</v>
+        <v>1192.762968068261</v>
       </c>
       <c r="R30" t="n">
-        <v>1044.405032933973</v>
+        <v>1044.485032933972</v>
       </c>
       <c r="S30" t="n">
-        <v>972.3579203339268</v>
+        <v>972.4379203339267</v>
       </c>
       <c r="T30" t="n">
-        <v>960.3657427747838</v>
+        <v>960.4457427747838</v>
       </c>
       <c r="U30" t="n">
-        <v>953.0905556718699</v>
+        <v>953.1705556718698</v>
       </c>
       <c r="V30" t="n">
-        <v>762.3601335469918</v>
+        <v>931.4426090137687</v>
       </c>
       <c r="W30" t="n">
-        <v>411.8550830419413</v>
+        <v>579.9274574986171</v>
       </c>
       <c r="X30" t="n">
-        <v>384.7210027940751</v>
+        <v>363.2041169807808</v>
       </c>
       <c r="Y30" t="n">
-        <v>378.2650505050505</v>
+        <v>356.7481646917562</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>672.9134037116369</v>
+        <v>1159.299226082725</v>
       </c>
       <c r="C31" t="n">
-        <v>672.9134037116369</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="D31" t="n">
-        <v>779.3025478366369</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="E31" t="n">
-        <v>779.3025478366369</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="F31" t="n">
-        <v>779.3025478366369</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="G31" t="n">
-        <v>892.2656259020774</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="H31" t="n">
-        <v>1055.741068766393</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="I31" t="n">
-        <v>1272.950431636902</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="J31" t="n">
-        <v>1272.950431636902</v>
+        <v>1276.950431636902</v>
       </c>
       <c r="K31" t="n">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="L31" t="n">
-        <v>1388</v>
+        <v>1376.308969736305</v>
       </c>
       <c r="M31" t="n">
-        <v>1275.068715092639</v>
+        <v>1263.377684828944</v>
       </c>
       <c r="N31" t="n">
-        <v>1110.693129870371</v>
+        <v>1099.002099606676</v>
       </c>
       <c r="O31" t="n">
-        <v>875.1658669324684</v>
+        <v>863.4748366687736</v>
       </c>
       <c r="P31" t="n">
-        <v>687.8052568109238</v>
+        <v>578.3895951217471</v>
       </c>
       <c r="Q31" t="n">
-        <v>360.1453917345622</v>
+        <v>250.7297300453855</v>
       </c>
       <c r="R31" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="S31" t="n">
-        <v>59.82252525810755</v>
+        <v>27.84</v>
       </c>
       <c r="T31" t="n">
-        <v>241.3953650726501</v>
+        <v>209.4128398145426</v>
       </c>
       <c r="U31" t="n">
-        <v>481.0220108256909</v>
+        <v>449.0394855675833</v>
       </c>
       <c r="V31" t="n">
-        <v>672.9134037116369</v>
+        <v>640.9308784535293</v>
       </c>
       <c r="W31" t="n">
-        <v>672.9134037116369</v>
+        <v>805.8917967132068</v>
       </c>
       <c r="X31" t="n">
-        <v>672.9134037116369</v>
+        <v>949.9925877374003</v>
       </c>
       <c r="Y31" t="n">
-        <v>672.9134037116369</v>
+        <v>1054.471888416433</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>72.44992162866241</v>
+        <v>70.07609493216536</v>
       </c>
       <c r="C32" t="n">
-        <v>32.5766102721029</v>
+        <v>29.19268256550484</v>
       </c>
       <c r="D32" t="n">
-        <v>32.23402871669907</v>
+        <v>27.84</v>
       </c>
       <c r="E32" t="n">
-        <v>32.23402871669907</v>
+        <v>27.84</v>
       </c>
       <c r="F32" t="n">
-        <v>32.23402871669907</v>
+        <v>27.84</v>
       </c>
       <c r="G32" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="H32" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="I32" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="J32" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="K32" t="n">
-        <v>56.03045587939699</v>
+        <v>56.19045587939698</v>
       </c>
       <c r="L32" t="n">
-        <v>398.5704558793969</v>
+        <v>91.36170331658292</v>
       </c>
       <c r="M32" t="n">
-        <v>667.154576173943</v>
+        <v>435.8817033165829</v>
       </c>
       <c r="N32" t="n">
-        <v>1009.694576173943</v>
+        <v>671.194576173943</v>
       </c>
       <c r="O32" t="n">
-        <v>1009.694576173943</v>
+        <v>1015.714576173943</v>
       </c>
       <c r="P32" t="n">
-        <v>1041.46</v>
+        <v>1047.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="R32" t="n">
-        <v>1384</v>
+        <v>1389.706981384311</v>
       </c>
       <c r="S32" t="n">
-        <v>1303.476648938316</v>
+        <v>1308.173529312526</v>
       </c>
       <c r="T32" t="n">
-        <v>1126.011907229854</v>
+        <v>1129.698686593963</v>
       </c>
       <c r="U32" t="n">
-        <v>884.3924259183798</v>
+        <v>887.0691042723877</v>
       </c>
       <c r="V32" t="n">
-        <v>662.3206843357293</v>
+        <v>663.9872616796363</v>
       </c>
       <c r="W32" t="n">
-        <v>431.6404055670954</v>
+        <v>432.2968819009013</v>
       </c>
       <c r="X32" t="n">
-        <v>247.5173414654108</v>
+        <v>247.1637167891158</v>
       </c>
       <c r="Y32" t="n">
-        <v>145.176500371667</v>
+        <v>143.8127746852709</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.68</v>
+        <v>379.3551515151515</v>
       </c>
       <c r="C33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="D33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="E33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="F33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="G33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="H33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="I33" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="J33" t="n">
-        <v>162.9028696092612</v>
+        <v>163.0628696092612</v>
       </c>
       <c r="K33" t="n">
-        <v>371.351671364022</v>
+        <v>371.5116713640219</v>
       </c>
       <c r="L33" t="n">
-        <v>668.5941820158259</v>
+        <v>668.7541820158258</v>
       </c>
       <c r="M33" t="n">
-        <v>784.8895237586852</v>
+        <v>785.049523758685</v>
       </c>
       <c r="N33" t="n">
-        <v>949.1843042153101</v>
+        <v>949.34430421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1216.598960427331</v>
+        <v>1216.758960427331</v>
       </c>
       <c r="P33" t="n">
-        <v>1351.899500368536</v>
+        <v>1352.059500368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1192.602968068261</v>
+        <v>1192.762968068261</v>
       </c>
       <c r="R33" t="n">
-        <v>1061.49675010569</v>
+        <v>1060.646649095589</v>
       </c>
       <c r="S33" t="n">
-        <v>749.2690332422511</v>
+        <v>1004.761152657159</v>
       </c>
       <c r="T33" t="n">
-        <v>749.2690332422511</v>
+        <v>1004.761152657159</v>
       </c>
       <c r="U33" t="n">
-        <v>749.2690332422511</v>
+        <v>1004.761152657159</v>
       </c>
       <c r="V33" t="n">
-        <v>399.7740837473016</v>
+        <v>765.4520023790062</v>
       </c>
       <c r="W33" t="n">
-        <v>377.1749494949495</v>
+        <v>741.8427671165532</v>
       </c>
       <c r="X33" t="n">
-        <v>27.68</v>
+        <v>730.8703030303031</v>
       </c>
       <c r="Y33" t="n">
-        <v>27.68</v>
+        <v>730.8703030303031</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>311.1533249451378</v>
+        <v>740.7943393459028</v>
       </c>
       <c r="C34" t="n">
-        <v>311.1533249451378</v>
+        <v>875.7063451643386</v>
       </c>
       <c r="D34" t="n">
-        <v>434.3724690701379</v>
+        <v>997.9354892893386</v>
       </c>
       <c r="E34" t="n">
-        <v>562.1013732815509</v>
+        <v>1124.674393500752</v>
       </c>
       <c r="F34" t="n">
-        <v>696.3623458734863</v>
+        <v>1257.945366092687</v>
       </c>
       <c r="G34" t="n">
-        <v>859.7688855308634</v>
+        <v>1257.945366092687</v>
       </c>
       <c r="H34" t="n">
-        <v>1040.074328395179</v>
+        <v>1257.945366092687</v>
       </c>
       <c r="I34" t="n">
-        <v>1040.074328395179</v>
+        <v>1257.945366092687</v>
       </c>
       <c r="J34" t="n">
-        <v>1382.614328395179</v>
+        <v>1257.945366092687</v>
       </c>
       <c r="K34" t="n">
-        <v>1382.614328395179</v>
+        <v>1388.834934455785</v>
       </c>
       <c r="L34" t="n">
-        <v>1382.614328395179</v>
+        <v>1388.834934455785</v>
       </c>
       <c r="M34" t="n">
-        <v>1286.854760659535</v>
+        <v>1292.06526571004</v>
       </c>
       <c r="N34" t="n">
-        <v>1139.650892608984</v>
+        <v>1143.851296649388</v>
       </c>
       <c r="O34" t="n">
-        <v>921.2953468427988</v>
+        <v>924.4856498731019</v>
       </c>
       <c r="P34" t="n">
-        <v>653.3818224674895</v>
+        <v>655.5620244876916</v>
       </c>
       <c r="Q34" t="n">
-        <v>342.8936745628451</v>
+        <v>344.0637755729461</v>
       </c>
       <c r="R34" t="n">
-        <v>27.68</v>
+        <v>27.84</v>
       </c>
       <c r="S34" t="n">
-        <v>76.57252525810755</v>
+        <v>34.1818507194447</v>
       </c>
       <c r="T34" t="n">
-        <v>274.9753650726501</v>
+        <v>231.5946905339873</v>
       </c>
       <c r="U34" t="n">
-        <v>311.1533249451378</v>
+        <v>231.5946905339873</v>
       </c>
       <c r="V34" t="n">
-        <v>311.1533249451378</v>
+        <v>439.3260834199332</v>
       </c>
       <c r="W34" t="n">
-        <v>311.1533249451378</v>
+        <v>620.1270016796107</v>
       </c>
       <c r="X34" t="n">
-        <v>311.1533249451378</v>
+        <v>620.1270016796107</v>
       </c>
       <c r="Y34" t="n">
-        <v>311.1533249451378</v>
+        <v>620.1270016796107</v>
       </c>
     </row>
     <row r="35">
@@ -6934,19 +6934,19 @@
         <v>55.39045587939698</v>
       </c>
       <c r="L35" t="n">
-        <v>390.0104558793969</v>
+        <v>90.56170331658292</v>
       </c>
       <c r="M35" t="n">
-        <v>650.994576173943</v>
+        <v>425.1817033165848</v>
       </c>
       <c r="N35" t="n">
-        <v>985.614576173943</v>
+        <v>759.8017033165867</v>
       </c>
       <c r="O35" t="n">
-        <v>985.614576173943</v>
+        <v>1094.421703316588</v>
       </c>
       <c r="P35" t="n">
-        <v>1017.38</v>
+        <v>1126.187127142646</v>
       </c>
       <c r="Q35" t="n">
         <v>1352</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>649.533061645696</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="C36" t="n">
-        <v>649.533061645696</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="D36" t="n">
-        <v>649.533061645696</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="E36" t="n">
-        <v>361.3882489209133</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="F36" t="n">
-        <v>361.3882489209133</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="G36" t="n">
-        <v>361.3882489209133</v>
+        <v>27.04</v>
       </c>
       <c r="H36" t="n">
         <v>27.04</v>
@@ -7046,13 +7046,13 @@
         <v>1010.516034281886</v>
       </c>
       <c r="W36" t="n">
-        <v>990.9472030598374</v>
+        <v>669.1018928677429</v>
       </c>
       <c r="X36" t="n">
-        <v>649.533061645696</v>
+        <v>327.6877514535996</v>
       </c>
       <c r="Y36" t="n">
-        <v>649.533061645696</v>
+        <v>327.6877514535996</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>469.3569907315228</v>
+        <v>551.8435352210107</v>
       </c>
       <c r="C37" t="n">
-        <v>608.2289965499587</v>
+        <v>690.7155410394465</v>
       </c>
       <c r="D37" t="n">
-        <v>734.4181406749587</v>
+        <v>792.4444046635247</v>
       </c>
       <c r="E37" t="n">
-        <v>865.1170448863718</v>
+        <v>792.4444046635247</v>
       </c>
       <c r="F37" t="n">
-        <v>1002.348017478307</v>
+        <v>792.4444046635247</v>
       </c>
       <c r="G37" t="n">
-        <v>1168.724557135684</v>
+        <v>792.4444046635247</v>
       </c>
       <c r="H37" t="n">
-        <v>1352</v>
+        <v>975.7198475278402</v>
       </c>
       <c r="I37" t="n">
-        <v>1352</v>
+        <v>1212.729210398349</v>
       </c>
       <c r="J37" t="n">
-        <v>1352</v>
+        <v>1212.729210398349</v>
       </c>
       <c r="K37" t="n">
-        <v>1352</v>
+        <v>1347.578778761447</v>
       </c>
       <c r="L37" t="n">
         <v>1352</v>
@@ -7101,37 +7101,37 @@
         <v>1115.097170274411</v>
       </c>
       <c r="O37" t="n">
-        <v>899.7719275385289</v>
+        <v>911.5644377518898</v>
       </c>
       <c r="P37" t="n">
-        <v>634.8887061935227</v>
+        <v>646.6812164068836</v>
       </c>
       <c r="Q37" t="n">
-        <v>327.4308613191813</v>
+        <v>339.2233715325421</v>
       </c>
       <c r="R37" t="n">
         <v>27.04</v>
       </c>
       <c r="S37" t="n">
-        <v>27.04</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="T37" t="n">
-        <v>27.04</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="U37" t="n">
-        <v>56.54956136200494</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="V37" t="n">
-        <v>56.54956136200494</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="W37" t="n">
-        <v>56.54956136200494</v>
+        <v>263.6634435177849</v>
       </c>
       <c r="X37" t="n">
-        <v>220.4503523861985</v>
+        <v>427.5642345419784</v>
       </c>
       <c r="Y37" t="n">
-        <v>344.7296530652307</v>
+        <v>551.8435352210107</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64.69234587108686</v>
+        <v>63.88300832625648</v>
       </c>
       <c r="C38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="D38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="E38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="F38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="G38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="H38" t="n">
-        <v>27.84933754483038</v>
+        <v>27.04</v>
       </c>
       <c r="I38" t="n">
         <v>27.04</v>
       </c>
       <c r="J38" t="n">
-        <v>361.66</v>
+        <v>361.6600000000091</v>
       </c>
       <c r="K38" t="n">
-        <v>390.010455879397</v>
+        <v>390.010455879406</v>
       </c>
       <c r="L38" t="n">
-        <v>425.1817033165829</v>
+        <v>425.181703316592</v>
       </c>
       <c r="M38" t="n">
-        <v>650.994576173943</v>
+        <v>759.8017033166011</v>
       </c>
       <c r="N38" t="n">
-        <v>985.614576173943</v>
+        <v>1094.42170331661</v>
       </c>
       <c r="O38" t="n">
-        <v>1320.234576173943</v>
+        <v>1094.42170331661</v>
       </c>
       <c r="P38" t="n">
-        <v>1352</v>
+        <v>1126.187127142667</v>
       </c>
       <c r="Q38" t="n">
         <v>1352</v>
       </c>
       <c r="R38" t="n">
-        <v>1352</v>
+        <v>1351.19066245517</v>
       </c>
       <c r="S38" t="n">
-        <v>1274.50695196862</v>
+        <v>1273.697614423789</v>
       </c>
       <c r="T38" t="n">
-        <v>1100.07251329046</v>
+        <v>1099.26317574563</v>
       </c>
       <c r="U38" t="n">
-        <v>861.483335009289</v>
+        <v>860.6739974644586</v>
       </c>
       <c r="V38" t="n">
-        <v>642.4418964569417</v>
+        <v>641.6325589121112</v>
       </c>
       <c r="W38" t="n">
-        <v>414.7919207186108</v>
+        <v>413.9825831737803</v>
       </c>
       <c r="X38" t="n">
-        <v>233.6991596472292</v>
+        <v>232.8898221023988</v>
       </c>
       <c r="Y38" t="n">
-        <v>134.3886215837884</v>
+        <v>133.579284038958</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>355.9481646917562</v>
+        <v>984.0151430139914</v>
       </c>
       <c r="C39" t="n">
-        <v>355.9481646917562</v>
+        <v>984.0151430139914</v>
       </c>
       <c r="D39" t="n">
-        <v>355.9481646917562</v>
+        <v>690.2964136126695</v>
       </c>
       <c r="E39" t="n">
-        <v>355.9481646917562</v>
+        <v>690.2964136126695</v>
       </c>
       <c r="F39" t="n">
-        <v>355.9481646917562</v>
+        <v>690.2964136126695</v>
       </c>
       <c r="G39" t="n">
-        <v>27.04</v>
+        <v>361.3882489209133</v>
       </c>
       <c r="H39" t="n">
         <v>27.04</v>
@@ -7280,16 +7280,16 @@
         <v>1012.041960737967</v>
       </c>
       <c r="V39" t="n">
-        <v>670.6278193238259</v>
+        <v>1010.516034281886</v>
       </c>
       <c r="W39" t="n">
-        <v>651.0589881017769</v>
+        <v>990.9472030598374</v>
       </c>
       <c r="X39" t="n">
-        <v>355.9481646917562</v>
+        <v>984.0151430139914</v>
       </c>
       <c r="Y39" t="n">
-        <v>355.9481646917562</v>
+        <v>984.0151430139914</v>
       </c>
     </row>
     <row r="40">
@@ -7299,16 +7299,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>951.8187246065984</v>
+        <v>962.8279932666121</v>
       </c>
       <c r="C40" t="n">
-        <v>1090.690730425034</v>
+        <v>962.8279932666121</v>
       </c>
       <c r="D40" t="n">
-        <v>1216.879874550034</v>
+        <v>1089.017137391612</v>
       </c>
       <c r="E40" t="n">
-        <v>1347.578778761447</v>
+        <v>1219.716041603025</v>
       </c>
       <c r="F40" t="n">
         <v>1347.578778761447</v>
@@ -7332,43 +7332,43 @@
         <v>1352</v>
       </c>
       <c r="M40" t="n">
-        <v>1271.06324550802</v>
+        <v>1259.270735294659</v>
       </c>
       <c r="N40" t="n">
-        <v>1126.889680487772</v>
+        <v>1115.097170274411</v>
       </c>
       <c r="O40" t="n">
-        <v>911.5644377518897</v>
+        <v>899.7719275385289</v>
       </c>
       <c r="P40" t="n">
-        <v>646.6812164068836</v>
+        <v>634.8887061935227</v>
       </c>
       <c r="Q40" t="n">
-        <v>339.2233715325421</v>
+        <v>327.4308613191813</v>
       </c>
       <c r="R40" t="n">
         <v>27.04</v>
       </c>
       <c r="S40" t="n">
-        <v>27.04</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="T40" t="n">
-        <v>27.04</v>
+        <v>78.90252525810754</v>
       </c>
       <c r="U40" t="n">
-        <v>266.8382847704895</v>
+        <v>338.3291710111483</v>
       </c>
       <c r="V40" t="n">
-        <v>478.5296776564354</v>
+        <v>550.0205638970942</v>
       </c>
       <c r="W40" t="n">
-        <v>663.2905959161128</v>
+        <v>550.0205638970942</v>
       </c>
       <c r="X40" t="n">
-        <v>827.1913869403063</v>
+        <v>713.9213549212877</v>
       </c>
       <c r="Y40" t="n">
-        <v>827.1913869403063</v>
+        <v>838.20065560032</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.04</v>
+        <v>370.2100453737412</v>
       </c>
       <c r="C41" t="n">
-        <v>27.04</v>
+        <v>232.3569360373837</v>
       </c>
       <c r="D41" t="n">
-        <v>27.04</v>
+        <v>213.4983025983266</v>
       </c>
       <c r="E41" t="n">
-        <v>27.04</v>
+        <v>213.4983025983266</v>
       </c>
       <c r="F41" t="n">
-        <v>27.04</v>
+        <v>120.680495822557</v>
       </c>
       <c r="G41" t="n">
-        <v>27.04</v>
+        <v>120.680495822557</v>
       </c>
       <c r="H41" t="n">
         <v>27.04</v>
@@ -7402,25 +7402,25 @@
         <v>27.04</v>
       </c>
       <c r="J41" t="n">
-        <v>361.66</v>
+        <v>27.04</v>
       </c>
       <c r="K41" t="n">
-        <v>696.2800000000001</v>
+        <v>55.39045587939698</v>
       </c>
       <c r="L41" t="n">
-        <v>731.451247437186</v>
+        <v>316.3745761738942</v>
       </c>
       <c r="M41" t="n">
-        <v>1066.071247437186</v>
+        <v>650.9945761739104</v>
       </c>
       <c r="N41" t="n">
-        <v>1320.234576173943</v>
+        <v>985.6145761739267</v>
       </c>
       <c r="O41" t="n">
-        <v>1320.234576173943</v>
+        <v>985.6145761739267</v>
       </c>
       <c r="P41" t="n">
-        <v>1352</v>
+        <v>1017.379999999984</v>
       </c>
       <c r="Q41" t="n">
         <v>1352</v>
@@ -7435,19 +7435,19 @@
         <v>1352</v>
       </c>
       <c r="U41" t="n">
-        <v>1328.881494188707</v>
+        <v>1352</v>
       </c>
       <c r="V41" t="n">
-        <v>1008.829954626259</v>
+        <v>1352</v>
       </c>
       <c r="W41" t="n">
-        <v>680.1698778778269</v>
+        <v>1023.339923251568</v>
       </c>
       <c r="X41" t="n">
-        <v>398.0670157963444</v>
+        <v>741.2370611700856</v>
       </c>
       <c r="Y41" t="n">
-        <v>197.7463767228026</v>
+        <v>540.9164220965438</v>
       </c>
     </row>
     <row r="42">
@@ -7578,7 +7578,7 @@
         <v>496.8655662474807</v>
       </c>
       <c r="P43" t="n">
-        <v>155.4514248333392</v>
+        <v>155.4514248333226</v>
       </c>
       <c r="Q43" t="n">
         <v>27.04</v>
@@ -7639,25 +7639,25 @@
         <v>27.04</v>
       </c>
       <c r="J44" t="n">
-        <v>361.66</v>
+        <v>27.04</v>
       </c>
       <c r="K44" t="n">
-        <v>390.010455879397</v>
+        <v>55.39045587939698</v>
       </c>
       <c r="L44" t="n">
-        <v>425.1817033165829</v>
+        <v>90.56170331658292</v>
       </c>
       <c r="M44" t="n">
-        <v>650.994576173943</v>
+        <v>425.1817033166136</v>
       </c>
       <c r="N44" t="n">
-        <v>985.614576173943</v>
+        <v>759.8017033166442</v>
       </c>
       <c r="O44" t="n">
-        <v>985.614576173943</v>
+        <v>1094.421703316675</v>
       </c>
       <c r="P44" t="n">
-        <v>1017.38</v>
+        <v>1126.187127142732</v>
       </c>
       <c r="Q44" t="n">
         <v>1352</v>
@@ -7666,22 +7666,22 @@
         <v>1352</v>
       </c>
       <c r="S44" t="n">
-        <v>1352</v>
+        <v>1166.426143887812</v>
       </c>
       <c r="T44" t="n">
-        <v>1352</v>
+        <v>883.910897128844</v>
       </c>
       <c r="U44" t="n">
-        <v>1010.585858585858</v>
+        <v>853.607982602531</v>
       </c>
       <c r="V44" t="n">
-        <v>1010.585858585858</v>
+        <v>853.607982602531</v>
       </c>
       <c r="W44" t="n">
-        <v>1010.585858585858</v>
+        <v>853.607982602531</v>
       </c>
       <c r="X44" t="n">
-        <v>1010.585858585858</v>
+        <v>853.607982602531</v>
       </c>
       <c r="Y44" t="n">
         <v>853.607982602531</v>
@@ -7742,7 +7742,7 @@
         <v>1352</v>
       </c>
       <c r="R45" t="n">
-        <v>1122.055777604276</v>
+        <v>1115.843276986924</v>
       </c>
       <c r="S45" t="n">
         <v>962.1298771254422</v>
@@ -7809,16 +7809,16 @@
         <v>1237.74305281103</v>
       </c>
       <c r="N46" t="n">
-        <v>985.4886797099741</v>
+        <v>1237.74305281103</v>
       </c>
       <c r="O46" t="n">
-        <v>662.082628893284</v>
+        <v>1106.447687728679</v>
       </c>
       <c r="P46" t="n">
-        <v>423.6194048993904</v>
+        <v>765.0335463142117</v>
       </c>
       <c r="Q46" t="n">
-        <v>82.20526348524891</v>
+        <v>423.6194048997132</v>
       </c>
       <c r="R46" t="n">
         <v>82.20526348524891</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>15.93574996368329</v>
+        <v>362.9357499636833</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>853.732037190056</v>
+        <v>504.732037190056</v>
       </c>
       <c r="N2" t="n">
-        <v>786.0792294266191</v>
+        <v>705.895690723</v>
       </c>
       <c r="O2" t="n">
-        <v>270.9661004182865</v>
+        <v>32.31673389570049</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>314.913713307013</v>
       </c>
       <c r="Q2" t="n">
-        <v>497.511649151606</v>
+        <v>495.511649151606</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>236.7301746033941</v>
       </c>
       <c r="M5" t="n">
-        <v>853.732037190056</v>
+        <v>851.732037190056</v>
       </c>
       <c r="N5" t="n">
-        <v>786.0792294266191</v>
+        <v>784.0792294266191</v>
       </c>
       <c r="O5" t="n">
-        <v>270.9661004182865</v>
+        <v>32.31673389570049</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>497.511649151606</v>
+        <v>495.511649151606</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>365.9357499636833</v>
+        <v>15.93574996368329</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>236.7301746033941</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>854.732037190056</v>
+        <v>851.732037190056</v>
       </c>
       <c r="N8" t="n">
-        <v>676.6881919088009</v>
+        <v>784.0792294266191</v>
       </c>
       <c r="O8" t="n">
         <v>32.31673389570049</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>498.511649151606</v>
+        <v>495.511649151606</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>373.9357499636833</v>
+        <v>372.9357499636835</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>752.0177673490052</v>
+        <v>861.7320371900561</v>
       </c>
       <c r="N11" t="n">
-        <v>795.0792294266191</v>
+        <v>794.0792294266193</v>
       </c>
       <c r="O11" t="n">
         <v>32.31673389570049</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>506.511649151606</v>
+        <v>394.837783350959</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>15.93574996368329</v>
+        <v>372.9357499636835</v>
       </c>
       <c r="K14" t="n">
-        <v>329.363175879397</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>862.732037190056</v>
+        <v>861.7320371900561</v>
       </c>
       <c r="N14" t="n">
-        <v>795.0792294266191</v>
+        <v>683.4053636259721</v>
       </c>
       <c r="O14" t="n">
         <v>32.31673389570049</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>424.4342034311585</v>
+        <v>505.5116491516062</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>373.9357499636833</v>
+        <v>372.9357499636835</v>
       </c>
       <c r="K17" t="n">
-        <v>329.363175879397</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>780.6545914696085</v>
+        <v>861.7320371900561</v>
       </c>
       <c r="N17" t="n">
-        <v>795.0792294266191</v>
+        <v>437.0792294266191</v>
       </c>
       <c r="O17" t="n">
-        <v>32.31673389570049</v>
+        <v>278.6428680950535</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>148.511649151606</v>
+        <v>505.5116491516062</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>15.93574996368329</v>
+        <v>297.7883967258505</v>
       </c>
       <c r="K20" t="n">
-        <v>329.363175879397</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>321.4734874371859</v>
       </c>
       <c r="M20" t="n">
-        <v>862.732037190056</v>
+        <v>861.7320371900561</v>
       </c>
       <c r="N20" t="n">
-        <v>795.0792294266191</v>
+        <v>794.0792294266193</v>
       </c>
       <c r="O20" t="n">
         <v>32.31673389570049</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>424.4342034311585</v>
+        <v>148.511649151606</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>373.9357499636833</v>
+        <v>372.9357499636835</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9632,10 +9632,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>752.0177673490052</v>
+        <v>861.7320371900561</v>
       </c>
       <c r="N23" t="n">
-        <v>795.0792294266191</v>
+        <v>683.4053636259721</v>
       </c>
       <c r="O23" t="n">
         <v>32.31673389570049</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>506.511649151606</v>
+        <v>505.5116491516062</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>362.9357499636833</v>
+        <v>363.9357499636833</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>741.46221179345</v>
+        <v>742.4218077530459</v>
       </c>
       <c r="N26" t="n">
-        <v>784.0792294266191</v>
+        <v>785.0792294266191</v>
       </c>
       <c r="O26" t="n">
         <v>32.31673389570049</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>495.511649151606</v>
+        <v>496.511649151606</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>15.93574996368329</v>
       </c>
       <c r="K29" t="n">
-        <v>318.363175879397</v>
+        <v>237.68977056299</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>851.732037190056</v>
+        <v>852.732037190056</v>
       </c>
       <c r="N29" t="n">
-        <v>702.4462281506162</v>
+        <v>785.0792294266191</v>
       </c>
       <c r="O29" t="n">
         <v>32.31673389570049</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>495.511649151606</v>
+        <v>496.511649151606</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,22 +10340,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>310.4734874371859</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>776.0291283966681</v>
+        <v>852.732037190056</v>
       </c>
       <c r="N32" t="n">
-        <v>783.0792294266191</v>
+        <v>674.7689999896091</v>
       </c>
       <c r="O32" t="n">
-        <v>32.31673389570049</v>
+        <v>380.3167338957005</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>494.511649151606</v>
+        <v>496.511649151606</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,22 +10577,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>302.4734874371859</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>768.3523607199004</v>
+        <v>842.7320371900579</v>
       </c>
       <c r="N35" t="n">
-        <v>775.0792294266191</v>
+        <v>775.0792294266209</v>
       </c>
       <c r="O35" t="n">
-        <v>32.31673389570049</v>
+        <v>370.3167338957024</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>486.511649151606</v>
+        <v>376.6054601186307</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>353.9357499636833</v>
+        <v>353.9357499636924</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10817,19 +10817,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>732.8258481570863</v>
+        <v>842.7320371900652</v>
       </c>
       <c r="N38" t="n">
-        <v>775.0792294266191</v>
+        <v>775.0792294266282</v>
       </c>
       <c r="O38" t="n">
-        <v>370.3167338957005</v>
+        <v>32.31673389570049</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>148.511649151606</v>
+        <v>376.6054601186089</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>353.9357499636833</v>
+        <v>15.93574996368329</v>
       </c>
       <c r="K41" t="n">
-        <v>309.363175879397</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>228.0938109669811</v>
       </c>
       <c r="M41" t="n">
-        <v>842.732037190056</v>
+        <v>842.7320371900724</v>
       </c>
       <c r="N41" t="n">
-        <v>693.8098645142525</v>
+        <v>775.0792294266355</v>
       </c>
       <c r="O41" t="n">
         <v>32.31673389570049</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>148.511649151606</v>
+        <v>486.5116491516225</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>353.9357499636833</v>
+        <v>15.93574996368329</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>732.8258481570863</v>
+        <v>842.732037190087</v>
       </c>
       <c r="N44" t="n">
-        <v>775.0792294266191</v>
+        <v>775.07922942665</v>
       </c>
       <c r="O44" t="n">
-        <v>32.31673389570049</v>
+        <v>370.3167338957315</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>486.511649151606</v>
+        <v>376.6054601185435</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22515,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.849111570467699</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22572,7 +22572,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.610711570467856</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.7473851112272314</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22800,13 +22800,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.610711570467799</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.849111570467841</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.7473851112272314</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.610711570467824</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.7473851112270022</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23229,7 +23229,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>7.339155739849787</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.704090864331428</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>25.41116740855523</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>19.24872080437399</v>
       </c>
     </row>
     <row r="12">
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.473505072284809</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23511,13 +23511,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>25.41116740855523</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>29.29196740855519</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.473505072284667</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.802711570467675</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.802711570467675</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24237,7 +24237,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.802711570467665</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -24420,13 +24420,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16.49015390440053</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>17.53224665887552</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>19.70409086433142</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,19 +24459,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>103.7181175510666</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>198.5010498574885</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>252.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>22.53411996105785</v>
       </c>
       <c r="M28" t="n">
-        <v>118.8019720582876</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24611,10 +24611,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>134.8665851112272</v>
       </c>
       <c r="R28" t="n">
-        <v>19.94541305293967</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24651,19 +24651,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>17.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>11.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>11.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>12.70409086433143</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>96.71811755106663</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>54.20488493842709</v>
       </c>
       <c r="U29" t="n">
-        <v>208.0999674085554</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>15.53411996105786</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24845,13 +24845,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>96.747385111227</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>108.400705072285</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -25316,7 +25316,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>11.67458511122729</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -25325,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>11.67458511122715</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>11.6745851112273</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25562,7 +25562,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>11.67458511122715</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25596,22 +25596,22 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>136.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>97.33915573984979</v>
+        <v>78.66910863518325</v>
       </c>
       <c r="E41" t="n">
         <v>91.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>91.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>90.53224665887551</v>
       </c>
       <c r="H41" t="n">
-        <v>92.70409086433143</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25650,10 +25650,10 @@
         <v>272.6900942913779</v>
       </c>
       <c r="U41" t="n">
-        <v>313.3159657451795</v>
+        <v>336.2032864983594</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>316.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25793,10 +25793,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>24.23438913155616</v>
+        <v>24.23438913153973</v>
       </c>
       <c r="Q43" t="n">
-        <v>277.2559558405922</v>
+        <v>277.2559558406086</v>
       </c>
       <c r="R43" t="n">
         <v>409.0615378172166</v>
@@ -25881,13 +25881,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>183.7181175510666</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>279.6900942913779</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>5.203286498358352</v>
+        <v>313.2034011173096</v>
       </c>
       <c r="V44" t="n">
         <v>323.8510241668239</v>
@@ -25899,7 +25899,7 @@
         <v>286.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>49.90933545931316</v>
+        <v>205.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.15037561117839</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>6.150375611178418</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -26024,19 +26024,19 @@
         <v>198.8019720582876</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>249.7318293700456</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>190.1895788769952</v>
       </c>
       <c r="P46" t="n">
-        <v>133.1557973776015</v>
+        <v>31.2343891312338</v>
       </c>
       <c r="Q46" t="n">
-        <v>73.38326642559799</v>
+        <v>73.38326642524453</v>
       </c>
       <c r="R46" t="n">
-        <v>416.0615378172166</v>
+        <v>78.06153781689693</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>843689.8475735132</v>
+        <v>843494.3137874996</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1536178.705651885</v>
+        <v>1536071.303534403</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2228977.910562085</v>
+        <v>2228648.293281307</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2921657.443654048</v>
+        <v>2921395.740136862</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3613202.314927829</v>
+        <v>3612724.859719689</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4305859.687110757</v>
+        <v>4305259.52919006</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4998517.05929368</v>
+        <v>4997794.198660429</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5691174.431476605</v>
+        <v>5690328.868130798</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6366741.671219429</v>
+        <v>6366400.901312168</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7048806.310962253</v>
+        <v>7048686.669038991</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7741321.850417911</v>
+        <v>7741344.041221921</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8432690.456259193</v>
+        <v>8432428.981608657</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9125193.723918658</v>
+        <v>9124932.249268122</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9748169.982196398</v>
+        <v>9747908.50754586</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10364524.19387489</v>
+        <v>10364262.71922435</v>
       </c>
     </row>
   </sheetData>
@@ -26269,34 +26269,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510884.781261903</v>
+        <v>1511077.068538699</v>
       </c>
       <c r="C2" t="n">
-        <v>1510884.781261903</v>
+        <v>1511077.068538699</v>
       </c>
       <c r="D2" t="n">
-        <v>1511252.448399114</v>
+        <v>1511077.068538699</v>
       </c>
       <c r="E2" t="n">
-        <v>1508825.173688249</v>
+        <v>1508354.442726167</v>
       </c>
       <c r="F2" t="n">
-        <v>1508825.173688249</v>
+        <v>1508354.442726167</v>
       </c>
       <c r="G2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510984.733389902</v>
       </c>
       <c r="H2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510984.733389902</v>
       </c>
       <c r="I2" t="n">
-        <v>1511252.448399113</v>
+        <v>1510984.733389903</v>
       </c>
       <c r="J2" t="n">
-        <v>1477368.872166167</v>
+        <v>1477851.333222167</v>
       </c>
       <c r="K2" t="n">
-        <v>1488141.032166167</v>
+        <v>1488623.493222167</v>
       </c>
       <c r="L2" t="n">
         <v>1511252.448399113</v>
@@ -26305,7 +26305,7 @@
         <v>1510916.220347911</v>
       </c>
       <c r="N2" t="n">
-        <v>1510916.220347911</v>
+        <v>1510916.22034791</v>
       </c>
       <c r="O2" t="n">
         <v>1359220.927151424</v>
@@ -26321,22 +26321,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183848</v>
+        <v>183944</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>318816</v>
+        <v>318720</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8000</v>
+        <v>8800</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>419776</v>
+        <v>418976</v>
       </c>
       <c r="K3" t="n">
         <v>5600</v>
@@ -26354,13 +26354,13 @@
         <v>21600</v>
       </c>
       <c r="M3" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>220800</v>
+        <v>220000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>666685.4019764792</v>
+        <v>666821.9624688199</v>
       </c>
       <c r="C4" t="n">
-        <v>664633.8172326065</v>
+        <v>664768.5980120352</v>
       </c>
       <c r="D4" t="n">
-        <v>662723.7481619717</v>
+        <v>662712.4480382029</v>
       </c>
       <c r="E4" t="n">
-        <v>659299.6330828893</v>
+        <v>659090.0316298932</v>
       </c>
       <c r="F4" t="n">
-        <v>657249.9752782211</v>
+        <v>657040.570073345</v>
       </c>
       <c r="G4" t="n">
-        <v>656328.7282867205</v>
+        <v>656216.3016803899</v>
       </c>
       <c r="H4" t="n">
-        <v>654268.7291913813</v>
+        <v>654156.101404266</v>
       </c>
       <c r="I4" t="n">
-        <v>652205.8543038694</v>
+        <v>652093.0250551179</v>
       </c>
       <c r="J4" t="n">
-        <v>634756.4875610447</v>
+        <v>634939.5868211564</v>
       </c>
       <c r="K4" t="n">
-        <v>637701.9681457884</v>
+        <v>637884.8466113596</v>
       </c>
       <c r="L4" t="n">
-        <v>646278.8764117826</v>
+        <v>646217.016809555</v>
       </c>
       <c r="M4" t="n">
-        <v>644220.4092816886</v>
+        <v>644205.0882793824</v>
       </c>
       <c r="N4" t="n">
-        <v>642129.1463396181</v>
+        <v>642113.8253373121</v>
       </c>
       <c r="O4" t="n">
-        <v>571415.6682646368</v>
+        <v>571400.3472623308</v>
       </c>
       <c r="P4" t="n">
-        <v>563074.2989092113</v>
+        <v>563058.9779069052</v>
       </c>
     </row>
     <row r="5">
@@ -26425,37 +26425,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56740.152</v>
+        <v>56702.621</v>
       </c>
       <c r="C5" t="n">
-        <v>56740.152</v>
+        <v>56702.621</v>
       </c>
       <c r="D5" t="n">
-        <v>56800.952</v>
+        <v>56702.621</v>
       </c>
       <c r="E5" t="n">
-        <v>56867.007</v>
+        <v>56806.207</v>
       </c>
       <c r="F5" t="n">
-        <v>56867.007</v>
+        <v>56806.207</v>
       </c>
       <c r="G5" t="n">
-        <v>57035.145</v>
+        <v>56974.345</v>
       </c>
       <c r="H5" t="n">
-        <v>57035.145</v>
+        <v>56974.345</v>
       </c>
       <c r="I5" t="n">
-        <v>57035.145</v>
+        <v>56974.345</v>
       </c>
       <c r="J5" t="n">
-        <v>54769.034</v>
+        <v>54829.834</v>
       </c>
       <c r="K5" t="n">
-        <v>55357.517</v>
+        <v>55418.317</v>
       </c>
       <c r="L5" t="n">
-        <v>56725.89</v>
+        <v>56763.421</v>
       </c>
       <c r="M5" t="n">
         <v>56491.697</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>603611.2272854238</v>
+        <v>603608.4850698791</v>
       </c>
       <c r="C6" t="n">
-        <v>789510.8120292965</v>
+        <v>789605.8495266635</v>
       </c>
       <c r="D6" t="n">
-        <v>791375.7482371427</v>
+        <v>791661.9995004961</v>
       </c>
       <c r="E6" t="n">
-        <v>473842.5336053597</v>
+        <v>473738.2040962739</v>
       </c>
       <c r="F6" t="n">
-        <v>794708.1914100281</v>
+        <v>794507.6656528219</v>
       </c>
       <c r="G6" t="n">
-        <v>789888.5751123932</v>
+        <v>788994.0867095123</v>
       </c>
       <c r="H6" t="n">
-        <v>799948.5742077325</v>
+        <v>799854.2869856365</v>
       </c>
       <c r="I6" t="n">
-        <v>802011.4490952441</v>
+        <v>801917.3633347847</v>
       </c>
       <c r="J6" t="n">
-        <v>368067.3506051225</v>
+        <v>369105.9124010109</v>
       </c>
       <c r="K6" t="n">
-        <v>789481.5470203785</v>
+        <v>789720.3296108074</v>
       </c>
       <c r="L6" t="n">
-        <v>786647.6819873304</v>
+        <v>786672.0105895585</v>
       </c>
       <c r="M6" t="n">
-        <v>807804.114066222</v>
+        <v>807019.4350685286</v>
       </c>
       <c r="N6" t="n">
-        <v>812295.3770082925</v>
+        <v>812310.6980105983</v>
       </c>
       <c r="O6" t="n">
-        <v>518920.4618867873</v>
+        <v>519735.7828890933</v>
       </c>
       <c r="P6" t="n">
-        <v>734202.2125711152</v>
+        <v>734217.5335734218</v>
       </c>
     </row>
   </sheetData>
@@ -26755,13 +26755,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E2" t="n">
         <v>403</v>
@@ -26785,7 +26785,7 @@
         <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M2" t="n">
         <v>413</v>
@@ -26859,37 +26859,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C4" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D4" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E4" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F4" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G4" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H4" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I4" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M4" t="n">
         <v>338</v>
@@ -26972,22 +26972,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26996,7 +26996,7 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
         <v>7</v>
@@ -27005,13 +27005,13 @@
         <v>27</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27076,16 +27076,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>338</v>
@@ -27204,7 +27204,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -27213,13 +27213,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27228,7 +27228,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -27317,16 +27317,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27433,13 +27433,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E2" t="n">
         <v>404.3632896068686</v>
@@ -27484,25 +27484,25 @@
         <v>236.737051089601</v>
       </c>
       <c r="S2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="V2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Y2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
@@ -27518,13 +27518,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0.9376868977026334</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27557,28 +27557,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>157.703566977272</v>
       </c>
       <c r="R3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T3" t="n">
-        <v>404.8722557835516</v>
+        <v>332.0186226051437</v>
       </c>
       <c r="U3" t="n">
         <v>400.2024352318849</v>
       </c>
       <c r="V3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W3" t="n">
-        <v>148.3509520155997</v>
+        <v>409</v>
       </c>
       <c r="X3" t="n">
-        <v>70.86273944538755</v>
+        <v>409</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,58 +27591,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>409</v>
       </c>
       <c r="C4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>409</v>
       </c>
       <c r="F4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
-        <v>244.9428892349727</v>
+        <v>409</v>
       </c>
       <c r="H4" t="n">
-        <v>408</v>
+        <v>227.8732900360448</v>
       </c>
       <c r="I4" t="n">
-        <v>408</v>
+        <v>173.5966031611019</v>
       </c>
       <c r="J4" t="n">
-        <v>82.87114972431928</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>327.8795667746313</v>
       </c>
       <c r="L4" t="n">
-        <v>408.0000000000005</v>
+        <v>409</v>
       </c>
       <c r="M4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T4" t="n">
         <v>209.5930910964217</v>
@@ -27654,13 +27654,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
@@ -27670,13 +27670,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E5" t="n">
         <v>404.3632896068686</v>
@@ -27721,25 +27721,25 @@
         <v>236.737051089601</v>
       </c>
       <c r="S5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="V5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Y5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6">
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.6190830448386</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>331.0047664317041</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>157.703566977272</v>
       </c>
       <c r="R6" t="n">
-        <v>408</v>
+        <v>192.7951557829453</v>
       </c>
       <c r="S6" t="n">
-        <v>408</v>
+        <v>117.3266414740453</v>
       </c>
       <c r="T6" t="n">
         <v>404.8722557835516</v>
@@ -27809,13 +27809,13 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V6" t="n">
-        <v>147.3587260609326</v>
+        <v>157.3883272267248</v>
       </c>
       <c r="W6" t="n">
-        <v>83.37314290982852</v>
+        <v>409</v>
       </c>
       <c r="X6" t="n">
-        <v>70.86273944538755</v>
+        <v>409</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,55 +27828,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I7" t="n">
-        <v>173.5966031611019</v>
+        <v>409</v>
       </c>
       <c r="J7" t="n">
-        <v>306.5591129177248</v>
+        <v>176.7951340706537</v>
       </c>
       <c r="K7" t="n">
         <v>276.7883147847496</v>
       </c>
       <c r="L7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S7" t="n">
         <v>360.6136108503964</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>408</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27907,13 +27907,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E8" t="n">
         <v>404.3632896068686</v>
@@ -27955,28 +27955,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>236.7053626600687</v>
+        <v>236.737051089601</v>
       </c>
       <c r="S8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="V8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Y8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -27995,10 +27995,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>271.7811507189476</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.6190830448386</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>189.7951557829453</v>
+        <v>409</v>
       </c>
       <c r="S9" t="n">
-        <v>114.3266414740453</v>
+        <v>159.2212017792411</v>
       </c>
       <c r="T9" t="n">
         <v>404.8722557835516</v>
@@ -28046,13 +28046,13 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V9" t="n">
-        <v>408</v>
+        <v>67.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X9" t="n">
-        <v>408</v>
+        <v>72.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,67 +28074,67 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>408</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G10" t="n">
-        <v>408</v>
+        <v>400.0258407310916</v>
       </c>
       <c r="H10" t="n">
-        <v>375.9000110899985</v>
+        <v>409</v>
       </c>
       <c r="I10" t="n">
-        <v>173.5966031611019</v>
+        <v>409</v>
       </c>
       <c r="J10" t="n">
-        <v>378.1294078523012</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K10" t="n">
-        <v>408</v>
+        <v>276.7883147847496</v>
       </c>
       <c r="L10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S10" t="n">
-        <v>408</v>
+        <v>360.6136108503964</v>
       </c>
       <c r="T10" t="n">
-        <v>209.5930910964217</v>
+        <v>409</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9528830777366</v>
+        <v>409</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>409</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>408</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>408</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28223,16 +28223,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>27.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>3.099912445519294</v>
+        <v>4.099912445519294</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>153.0766483193154</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28244,7 +28244,7 @@
         <v>331.0047664317041</v>
       </c>
       <c r="I12" t="n">
-        <v>212.9792160800278</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>157.703566977272</v>
       </c>
       <c r="R12" t="n">
         <v>403</v>
@@ -28283,7 +28283,7 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V12" t="n">
-        <v>403</v>
+        <v>276.742513302456</v>
       </c>
       <c r="W12" t="n">
         <v>403</v>
@@ -28305,16 +28305,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C13" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D13" t="n">
         <v>403</v>
       </c>
-      <c r="D13" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E13" t="n">
-        <v>280.9809048369565</v>
+        <v>403</v>
       </c>
       <c r="F13" t="n">
-        <v>274.3828559677419</v>
+        <v>403</v>
       </c>
       <c r="G13" t="n">
         <v>244.9428892349727</v>
@@ -28323,13 +28323,13 @@
         <v>227.8732900360448</v>
       </c>
       <c r="I13" t="n">
+        <v>272.836694675235</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28.1294078523012</v>
+      </c>
+      <c r="K13" t="n">
         <v>403</v>
-      </c>
-      <c r="J13" t="n">
-        <v>386.1294078523012</v>
-      </c>
-      <c r="K13" t="n">
-        <v>276.7883147847496</v>
       </c>
       <c r="L13" t="n">
         <v>403</v>
@@ -28353,16 +28353,16 @@
         <v>403</v>
       </c>
       <c r="S13" t="n">
-        <v>360.6136108503964</v>
+        <v>403</v>
       </c>
       <c r="T13" t="n">
-        <v>209.5930910964217</v>
+        <v>403</v>
       </c>
       <c r="U13" t="n">
-        <v>314.3812872427307</v>
+        <v>403</v>
       </c>
       <c r="V13" t="n">
-        <v>403</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W13" t="n">
         <v>403</v>
@@ -28469,19 +28469,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>325.6190830448386</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>331.0047664317041</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>212.9792160800278</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,16 +28508,16 @@
         <v>157.703566977272</v>
       </c>
       <c r="R15" t="n">
-        <v>181.7951557829453</v>
+        <v>313.727836015134</v>
       </c>
       <c r="S15" t="n">
-        <v>141.9473575195105</v>
+        <v>107.3266414740453</v>
       </c>
       <c r="T15" t="n">
         <v>403</v>
       </c>
       <c r="U15" t="n">
-        <v>42.20243523188486</v>
+        <v>400.2024352318849</v>
       </c>
       <c r="V15" t="n">
         <v>403</v>
@@ -28542,16 +28542,16 @@
         <v>403</v>
       </c>
       <c r="C16" t="n">
-        <v>403</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
-        <v>403</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
         <v>403</v>
       </c>
       <c r="F16" t="n">
-        <v>403</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G16" t="n">
         <v>403</v>
@@ -28563,10 +28563,10 @@
         <v>173.5966031611019</v>
       </c>
       <c r="J16" t="n">
-        <v>342.889736804431</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K16" t="n">
-        <v>403</v>
+        <v>276.7883147847496</v>
       </c>
       <c r="L16" t="n">
         <v>403</v>
@@ -28593,22 +28593,22 @@
         <v>360.6136108503964</v>
       </c>
       <c r="T16" t="n">
-        <v>209.5930910964217</v>
+        <v>323.6114444934196</v>
       </c>
       <c r="U16" t="n">
-        <v>150.9528830777366</v>
+        <v>403</v>
       </c>
       <c r="V16" t="n">
         <v>403</v>
       </c>
       <c r="W16" t="n">
-        <v>226.3728098387097</v>
+        <v>403</v>
       </c>
       <c r="X16" t="n">
-        <v>247.4436454301076</v>
+        <v>403</v>
       </c>
       <c r="Y16" t="n">
-        <v>287.4653528494624</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17">
@@ -28627,19 +28627,19 @@
         <v>405</v>
       </c>
       <c r="E17" t="n">
-        <v>404.3632896068686</v>
+        <v>405</v>
       </c>
       <c r="F17" t="n">
-        <v>404.8896287080118</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>403.5322466588755</v>
+        <v>403.613923026617</v>
       </c>
       <c r="H17" t="n">
         <v>405</v>
       </c>
       <c r="I17" t="n">
-        <v>141.0280063385893</v>
+        <v>141.4020039037901</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>56.35600927952999</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -28718,7 +28718,7 @@
         <v>331.0047664317041</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>212.9792160800278</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,16 +28745,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>181.7951557829453</v>
+        <v>182.7951557829453</v>
       </c>
       <c r="S18" t="n">
         <v>405</v>
       </c>
       <c r="T18" t="n">
-        <v>404.8722557835516</v>
+        <v>47.87225578355155</v>
       </c>
       <c r="U18" t="n">
-        <v>42.20243523188486</v>
+        <v>400.2024352318849</v>
       </c>
       <c r="V18" t="n">
         <v>405</v>
@@ -28766,7 +28766,7 @@
         <v>405</v>
       </c>
       <c r="Y18" t="n">
-        <v>286.1700614793654</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -28776,19 +28776,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>405</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C19" t="n">
-        <v>328.2772334724779</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D19" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E19" t="n">
-        <v>405</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F19" t="n">
-        <v>405</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G19" t="n">
         <v>244.9428892349727</v>
@@ -28797,10 +28797,10 @@
         <v>227.8732900360448</v>
       </c>
       <c r="I19" t="n">
-        <v>173.5966031611019</v>
+        <v>405</v>
       </c>
       <c r="J19" t="n">
-        <v>28.1294078523012</v>
+        <v>163.7078936853063</v>
       </c>
       <c r="K19" t="n">
         <v>276.7883147847496</v>
@@ -28839,13 +28839,13 @@
         <v>405</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>405</v>
       </c>
       <c r="X19" t="n">
         <v>405</v>
       </c>
       <c r="Y19" t="n">
-        <v>405</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="20">
@@ -28864,13 +28864,13 @@
         <v>405</v>
       </c>
       <c r="E20" t="n">
-        <v>404.3632896068686</v>
+        <v>405</v>
       </c>
       <c r="F20" t="n">
-        <v>404.8896287080118</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>403.5322466588755</v>
+        <v>403.613923026617</v>
       </c>
       <c r="H20" t="n">
         <v>405</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>236.3630535244001</v>
+        <v>236.737051089601</v>
       </c>
       <c r="S20" t="n">
         <v>405</v>
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>27.55655664632641</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>23.67373694169584</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28994,13 +28994,13 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V21" t="n">
-        <v>56.51066719152016</v>
+        <v>405</v>
       </c>
       <c r="W21" t="n">
         <v>405</v>
       </c>
       <c r="X21" t="n">
-        <v>401.7352545265688</v>
+        <v>405</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -29016,28 +29016,28 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C22" t="n">
-        <v>272.7252466480447</v>
+        <v>405</v>
       </c>
       <c r="D22" t="n">
-        <v>285.5362180555555</v>
+        <v>405</v>
       </c>
       <c r="E22" t="n">
-        <v>280.9809048369565</v>
+        <v>405</v>
       </c>
       <c r="F22" t="n">
         <v>405</v>
       </c>
       <c r="G22" t="n">
-        <v>244.9428892349727</v>
+        <v>405</v>
       </c>
       <c r="H22" t="n">
         <v>405</v>
       </c>
       <c r="I22" t="n">
-        <v>405</v>
+        <v>203.2754657378792</v>
       </c>
       <c r="J22" t="n">
-        <v>386.1294078523012</v>
+        <v>385.1294078523013</v>
       </c>
       <c r="K22" t="n">
         <v>405</v>
@@ -29067,10 +29067,10 @@
         <v>405</v>
       </c>
       <c r="T22" t="n">
-        <v>288.6361811365081</v>
+        <v>209.5930910964217</v>
       </c>
       <c r="U22" t="n">
-        <v>405</v>
+        <v>150.9528830777366</v>
       </c>
       <c r="V22" t="n">
         <v>199.1703102162162</v>
@@ -29104,10 +29104,10 @@
         <v>404.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>404.515631142811</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>403.5322466588755</v>
+        <v>404.2506334197483</v>
       </c>
       <c r="H23" t="n">
         <v>405</v>
@@ -29171,28 +29171,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>27.55655664632641</v>
       </c>
       <c r="C24" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>305.0840537192949</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>325.6190830448386</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>331.0047664317041</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>212.9792160800278</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29216,16 +29216,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>157.703566977272</v>
       </c>
       <c r="R24" t="n">
-        <v>181.7951557829453</v>
+        <v>405</v>
       </c>
       <c r="S24" t="n">
-        <v>106.3266414740453</v>
+        <v>405</v>
       </c>
       <c r="T24" t="n">
-        <v>232.3242830227374</v>
+        <v>404.8722557835516</v>
       </c>
       <c r="U24" t="n">
         <v>400.2024352318849</v>
@@ -29250,19 +29250,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>287.1138003370787</v>
+        <v>405</v>
       </c>
       <c r="C25" t="n">
-        <v>272.7252466480447</v>
+        <v>405</v>
       </c>
       <c r="D25" t="n">
-        <v>405</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E25" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F25" t="n">
-        <v>405</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G25" t="n">
         <v>405</v>
@@ -29271,10 +29271,10 @@
         <v>227.8732900360448</v>
       </c>
       <c r="I25" t="n">
-        <v>405</v>
+        <v>173.5966031611019</v>
       </c>
       <c r="J25" t="n">
-        <v>325.0282764875552</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K25" t="n">
         <v>405</v>
@@ -29307,10 +29307,10 @@
         <v>209.5930910964217</v>
       </c>
       <c r="U25" t="n">
-        <v>150.9528830777366</v>
+        <v>355.8107845793933</v>
       </c>
       <c r="V25" t="n">
-        <v>199.1703102162162</v>
+        <v>405</v>
       </c>
       <c r="W25" t="n">
         <v>405</v>
@@ -29319,7 +29319,7 @@
         <v>405</v>
       </c>
       <c r="Y25" t="n">
-        <v>287.4653528494624</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26">
@@ -29408,10 +29408,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>141.5222891006395</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>14.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29423,7 +29423,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>325.6190830448386</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>331.0047664317041</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>157.703566977272</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>386</v>
@@ -29468,16 +29468,16 @@
         <v>386</v>
       </c>
       <c r="V27" t="n">
-        <v>386</v>
+        <v>66.51066719152018</v>
       </c>
       <c r="W27" t="n">
         <v>386</v>
       </c>
       <c r="X27" t="n">
+        <v>265.1691080510381</v>
+      </c>
+      <c r="Y27" t="n">
         <v>386</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>52.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -29508,10 +29508,10 @@
         <v>386</v>
       </c>
       <c r="I28" t="n">
-        <v>173.5966031611019</v>
+        <v>386</v>
       </c>
       <c r="J28" t="n">
-        <v>62.19128512448987</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K28" t="n">
         <v>386</v>
@@ -29544,10 +29544,10 @@
         <v>386</v>
       </c>
       <c r="U28" t="n">
-        <v>150.9528830777366</v>
+        <v>163.4006492544068</v>
       </c>
       <c r="V28" t="n">
-        <v>386</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W28" t="n">
         <v>386</v>
@@ -29651,7 +29651,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9376868977026334</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29660,7 +29660,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.6190830448386</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>331.0047664317041</v>
@@ -29705,13 +29705,13 @@
         <v>393</v>
       </c>
       <c r="V30" t="n">
-        <v>225.6875492878909</v>
+        <v>393</v>
       </c>
       <c r="W30" t="n">
-        <v>85.37314290982852</v>
+        <v>84.37314290982854</v>
       </c>
       <c r="X30" t="n">
-        <v>393</v>
+        <v>205.3066323327296</v>
       </c>
       <c r="Y30" t="n">
         <v>393</v>
@@ -29724,13 +29724,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>287.1138003370787</v>
+        <v>393</v>
       </c>
       <c r="C31" t="n">
-        <v>272.7252466480447</v>
+        <v>391.5648482179207</v>
       </c>
       <c r="D31" t="n">
-        <v>393</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E31" t="n">
         <v>280.9809048369565</v>
@@ -29739,13 +29739,13 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G31" t="n">
-        <v>359.0470084929934</v>
+        <v>244.9428892349727</v>
       </c>
       <c r="H31" t="n">
-        <v>393</v>
+        <v>227.8732900360448</v>
       </c>
       <c r="I31" t="n">
-        <v>393</v>
+        <v>173.5966031611019</v>
       </c>
       <c r="J31" t="n">
         <v>28.1294078523012</v>
@@ -29775,7 +29775,7 @@
         <v>393</v>
       </c>
       <c r="S31" t="n">
-        <v>393</v>
+        <v>360.6136108503964</v>
       </c>
       <c r="T31" t="n">
         <v>393</v>
@@ -29787,13 +29787,13 @@
         <v>393</v>
       </c>
       <c r="W31" t="n">
-        <v>226.3728098387097</v>
+        <v>393</v>
       </c>
       <c r="X31" t="n">
-        <v>247.4436454301076</v>
+        <v>393</v>
       </c>
       <c r="Y31" t="n">
-        <v>287.4653528494624</v>
+        <v>393</v>
       </c>
     </row>
     <row r="32">
@@ -29803,13 +29803,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E32" t="n">
         <v>404.3632896068686</v>
@@ -29818,7 +29818,7 @@
         <v>404.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>399.0237582293435</v>
+        <v>403.5322466588755</v>
       </c>
       <c r="H32" t="n">
         <v>405.7040908643314</v>
@@ -29851,28 +29851,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>236.737051089601</v>
+        <v>234.4669626600688</v>
       </c>
       <c r="S32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="T32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="V32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="W32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="X32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y32" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33">
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>36.55655664632658</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>13.09991244551931</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29930,10 +29930,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="S33" t="n">
-        <v>155.2212017792409</v>
+        <v>409</v>
       </c>
       <c r="T33" t="n">
         <v>404.8722557835516</v>
@@ -29942,13 +29942,13 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V33" t="n">
-        <v>68.51066719152016</v>
+        <v>177.5946084161488</v>
       </c>
       <c r="W33" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="X33" t="n">
-        <v>73.86273944538755</v>
+        <v>409</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29961,70 +29961,70 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>409</v>
       </c>
       <c r="C34" t="n">
-        <v>272.7252466480447</v>
+        <v>409</v>
       </c>
       <c r="D34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G34" t="n">
-        <v>410</v>
+        <v>244.9428892349727</v>
       </c>
       <c r="H34" t="n">
-        <v>410</v>
+        <v>227.8732900360448</v>
       </c>
       <c r="I34" t="n">
         <v>173.5966031611019</v>
       </c>
       <c r="J34" t="n">
-        <v>374.1294078523013</v>
+        <v>28.1294078523012</v>
       </c>
       <c r="K34" t="n">
-        <v>276.7883147847496</v>
+        <v>409</v>
       </c>
       <c r="L34" t="n">
         <v>408.5341199610579</v>
       </c>
       <c r="M34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="R34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="S34" t="n">
-        <v>410</v>
+        <v>367.0195206680173</v>
       </c>
       <c r="T34" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U34" t="n">
-        <v>187.4962768883303</v>
+        <v>150.9528830777366</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>409</v>
       </c>
       <c r="W34" t="n">
-        <v>226.3728098387097</v>
+        <v>409</v>
       </c>
       <c r="X34" t="n">
         <v>247.4436454301076</v>
@@ -30128,16 +30128,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>57.40873262437782</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.6190830448386</v>
+        <v>27.97780910577512</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>331.0047664317041</v>
       </c>
       <c r="I36" t="n">
         <v>212.9792160800278</v>
@@ -30182,10 +30182,10 @@
         <v>413</v>
       </c>
       <c r="W36" t="n">
-        <v>413</v>
+        <v>94.37314290982667</v>
       </c>
       <c r="X36" t="n">
-        <v>81.86273944538755</v>
+        <v>81.8627394453857</v>
       </c>
       <c r="Y36" t="n">
         <v>399.3913927661343</v>
@@ -30198,37 +30198,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>413</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>413</v>
       </c>
       <c r="D37" t="n">
-        <v>413</v>
+        <v>388.2926459586647</v>
       </c>
       <c r="E37" t="n">
-        <v>413</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
-        <v>413</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>413</v>
+        <v>244.9428892349727</v>
       </c>
       <c r="H37" t="n">
         <v>413</v>
       </c>
       <c r="I37" t="n">
-        <v>173.5966031611019</v>
+        <v>413</v>
       </c>
       <c r="J37" t="n">
         <v>28.1294078523012</v>
       </c>
       <c r="K37" t="n">
-        <v>276.7883147847496</v>
+        <v>413</v>
       </c>
       <c r="L37" t="n">
-        <v>408.5341199610579</v>
+        <v>413</v>
       </c>
       <c r="M37" t="n">
         <v>413</v>
@@ -30249,19 +30249,19 @@
         <v>413</v>
       </c>
       <c r="S37" t="n">
-        <v>360.6136108503964</v>
+        <v>413</v>
       </c>
       <c r="T37" t="n">
         <v>209.5930910964217</v>
       </c>
       <c r="U37" t="n">
-        <v>180.7605208171356</v>
+        <v>150.9528830777366</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>413</v>
       </c>
       <c r="X37" t="n">
         <v>413</v>
@@ -30298,7 +30298,7 @@
         <v>405.7040908643314</v>
       </c>
       <c r="I38" t="n">
-        <v>140.6007597344081</v>
+        <v>141.4020039037901</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>236.737051089601</v>
+        <v>235.9358069202189</v>
       </c>
       <c r="S38" t="n">
         <v>413</v>
@@ -30362,7 +30362,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>57.15614479039397</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30374,7 +30374,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>331.0047664317041</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>212.9792160800278</v>
@@ -30416,13 +30416,13 @@
         <v>400.2024352318849</v>
       </c>
       <c r="V39" t="n">
-        <v>76.51066719152016</v>
+        <v>413</v>
       </c>
       <c r="W39" t="n">
         <v>413</v>
       </c>
       <c r="X39" t="n">
-        <v>127.7030242694671</v>
+        <v>413</v>
       </c>
       <c r="Y39" t="n">
         <v>399.3913927661343</v>
@@ -30438,7 +30438,7 @@
         <v>413</v>
       </c>
       <c r="C40" t="n">
-        <v>413</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
         <v>413</v>
@@ -30447,7 +30447,7 @@
         <v>413</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>403.5371359257441</v>
       </c>
       <c r="G40" t="n">
         <v>244.9428892349727</v>
@@ -30486,25 +30486,25 @@
         <v>413</v>
       </c>
       <c r="S40" t="n">
-        <v>360.6136108503964</v>
+        <v>413</v>
       </c>
       <c r="T40" t="n">
         <v>209.5930910964217</v>
       </c>
       <c r="U40" t="n">
-        <v>393.1733727448977</v>
+        <v>413</v>
       </c>
       <c r="V40" t="n">
         <v>413</v>
       </c>
       <c r="W40" t="n">
-        <v>413</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>413</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41">
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>28.63682412060301</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L2" t="n">
-        <v>35.52651256281408</v>
+        <v>35.5265125628141</v>
       </c>
       <c r="M2" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>349</v>
+        <v>268.8164612963809</v>
       </c>
       <c r="O2" t="n">
-        <v>238.649366522586</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>32.08628669298693</v>
+        <v>347</v>
       </c>
       <c r="Q2" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>121.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>135.2747533519553</v>
+        <v>136.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4637819444445</v>
+        <v>123.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>128.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>133.6171440322581</v>
+        <v>134.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>164.0571107650273</v>
       </c>
       <c r="H4" t="n">
-        <v>180.1267099639552</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>234.4033968388981</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>54.74174187201807</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>131.2116852152504</v>
+        <v>51.09125198988166</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.4658800389421458</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>47.38638914960359</v>
+        <v>48.38638914960359</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -34940,13 +34940,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>181.6271901612903</v>
+        <v>182.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>160.5563545698924</v>
+        <v>161.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>121.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,25 +34983,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>28.63682412060301</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L5" t="n">
-        <v>35.52651256281408</v>
+        <v>272.2566871662082</v>
       </c>
       <c r="M5" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N5" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O5" t="n">
-        <v>238.649366522586</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q5" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120.8861996629213</v>
+        <v>121.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>135.2747533519553</v>
+        <v>136.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>122.4637819444445</v>
+        <v>123.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>127.0190951630435</v>
+        <v>128.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>133.6171440322581</v>
+        <v>134.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>163.0571107650273</v>
+        <v>164.0571107650273</v>
       </c>
       <c r="H7" t="n">
-        <v>180.1267099639552</v>
+        <v>181.1267099639552</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>235.4033968388981</v>
       </c>
       <c r="J7" t="n">
-        <v>278.4297050654236</v>
+        <v>148.6657262183525</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.4658800389421458</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35183,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>120.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>28.63682412060302</v>
+        <v>265.3669987239971</v>
       </c>
       <c r="L8" t="n">
         <v>35.5265125628141</v>
       </c>
       <c r="M8" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="N8" t="n">
-        <v>239.6089624821819</v>
+        <v>347</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q8" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35360,28 +35360,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>127.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>133.6171440322581</v>
+        <v>134.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>163.0571107650273</v>
+        <v>155.0829514961189</v>
       </c>
       <c r="H10" t="n">
-        <v>148.0267210539537</v>
+        <v>181.1267099639552</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>235.4033968388981</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>131.2116852152504</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.4658800389421405</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>47.38638914960359</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>199.4069089035783</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>258.0471169222634</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>209.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>160.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>120.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="K11" t="n">
         <v>28.63682412060302</v>
       </c>
       <c r="L11" t="n">
-        <v>35.5265125628141</v>
+        <v>35.52651256281405</v>
       </c>
       <c r="M11" t="n">
-        <v>247.2857301589493</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="N11" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q11" t="n">
-        <v>358</v>
+        <v>246.326134199353</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35591,16 +35591,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>130.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>117.4637819444445</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>122.0190951630435</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>128.6171440322581</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -35609,13 +35609,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>229.4033968388981</v>
+        <v>99.2400915141331</v>
       </c>
       <c r="J13" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>126.2116852152504</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35639,16 +35639,16 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>42.38638914960358</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>193.4069089035783</v>
       </c>
       <c r="U13" t="n">
-        <v>163.428404164994</v>
+        <v>252.0471169222634</v>
       </c>
       <c r="V13" t="n">
-        <v>203.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>176.6271901612903</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L14" t="n">
-        <v>35.5265125628141</v>
+        <v>35.52651256281405</v>
       </c>
       <c r="M14" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>358</v>
+        <v>246.326134199353</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q14" t="n">
-        <v>275.9225542795525</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35828,16 +35828,16 @@
         <v>115.8861996629213</v>
       </c>
       <c r="C16" t="n">
-        <v>130.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>117.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>122.0190951630435</v>
       </c>
       <c r="F16" t="n">
-        <v>128.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>158.0571107650273</v>
@@ -35849,10 +35849,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>314.7603289521298</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>126.2116852152504</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,22 +35879,22 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>114.0183533969979</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>252.0471169222634</v>
       </c>
       <c r="V16" t="n">
         <v>203.8296897837838</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>176.6271901612903</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>155.5563545698924</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>115.5346471505376</v>
       </c>
     </row>
     <row r="17">
@@ -35913,13 +35913,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.6367103931313522</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.08167636774144549</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="K17" t="n">
-        <v>358</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L17" t="n">
-        <v>35.5265125628141</v>
+        <v>35.52651256281405</v>
       </c>
       <c r="M17" t="n">
-        <v>275.9225542795525</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="N17" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>246.326134199353</v>
       </c>
       <c r="P17" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36062,19 +36062,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>117.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55.55198682443323</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>124.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>130.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -36083,10 +36083,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>231.4033968388981</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>135.5784858330051</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -36125,13 +36125,13 @@
         <v>205.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>178.6271901612903</v>
       </c>
       <c r="X19" t="n">
         <v>157.5563545698924</v>
       </c>
       <c r="Y19" t="n">
-        <v>117.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -36150,13 +36150,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.6367103931313522</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.08167636774144549</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>281.8526467621672</v>
       </c>
       <c r="K20" t="n">
-        <v>358</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L20" t="n">
-        <v>35.5265125628141</v>
+        <v>357</v>
       </c>
       <c r="M20" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="N20" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q20" t="n">
-        <v>275.9225542795525</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36302,28 +36302,28 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>132.2747533519553</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>119.4637819444445</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>124.0190951630435</v>
       </c>
       <c r="F22" t="n">
         <v>130.6171440322581</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>160.0571107650273</v>
       </c>
       <c r="H22" t="n">
         <v>177.1267099639552</v>
       </c>
       <c r="I22" t="n">
-        <v>231.4033968388981</v>
+        <v>29.67886257677726</v>
       </c>
       <c r="J22" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="K22" t="n">
         <v>128.2116852152504</v>
@@ -36350,13 +36350,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>44.38638914960359</v>
+        <v>44.38638914960358</v>
       </c>
       <c r="T22" t="n">
-        <v>79.04309004008643</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>254.0471169222634</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -36393,7 +36393,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.7183867608727899</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="K23" t="n">
         <v>28.63682412060302</v>
       </c>
       <c r="L23" t="n">
-        <v>35.5265125628141</v>
+        <v>35.52651256281405</v>
       </c>
       <c r="M23" t="n">
-        <v>247.2857301589493</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="N23" t="n">
-        <v>358</v>
+        <v>246.326134199353</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q23" t="n">
-        <v>358</v>
+        <v>357.0000000000002</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36536,19 +36536,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>117.8861996629213</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>132.2747533519553</v>
       </c>
       <c r="D25" t="n">
-        <v>119.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>130.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>160.0571107650273</v>
@@ -36557,10 +36557,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>231.4033968388981</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>296.898868635254</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>128.2116852152504</v>
@@ -36593,10 +36593,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>204.8579015016567</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>205.8296897837838</v>
       </c>
       <c r="W25" t="n">
         <v>178.6271901612903</v>
@@ -36605,7 +36605,7 @@
         <v>157.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>117.5346471505376</v>
       </c>
     </row>
     <row r="26">
@@ -36639,7 +36639,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K26" t="n">
         <v>28.63682412060302</v>
@@ -36648,10 +36648,10 @@
         <v>35.5265125628141</v>
       </c>
       <c r="M26" t="n">
-        <v>236.730174603394</v>
+        <v>237.68977056299</v>
       </c>
       <c r="N26" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -36660,7 +36660,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q26" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36794,10 +36794,10 @@
         <v>158.1267099639552</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>212.4033968388981</v>
       </c>
       <c r="J28" t="n">
-        <v>34.06187727218867</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>109.2116852152504</v>
@@ -36830,10 +36830,10 @@
         <v>176.4069089035783</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>12.44776617667016</v>
       </c>
       <c r="V28" t="n">
-        <v>186.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>159.6271901612903</v>
@@ -36879,16 +36879,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>347</v>
+        <v>266.326594683593</v>
       </c>
       <c r="L29" t="n">
-        <v>35.5265125628141</v>
+        <v>35.52651256281405</v>
       </c>
       <c r="M29" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N29" t="n">
-        <v>265.366998723997</v>
+        <v>348</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q29" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37010,13 +37010,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>105.8861996629213</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>118.8396015698761</v>
       </c>
       <c r="D31" t="n">
-        <v>107.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -37025,13 +37025,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>114.1041192580207</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>165.1267099639552</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>219.4033968388981</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -37061,7 +37061,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>32.38638914960358</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>183.4069089035783</v>
@@ -37073,13 +37073,13 @@
         <v>193.8296897837838</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>166.6271901612903</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>145.5563545698924</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>105.5346471505376</v>
       </c>
     </row>
     <row r="32">
@@ -37116,25 +37116,25 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>28.63682412060302</v>
+        <v>28.63682412060301</v>
       </c>
       <c r="L32" t="n">
-        <v>346</v>
+        <v>35.52651256281408</v>
       </c>
       <c r="M32" t="n">
-        <v>271.2970912066122</v>
+        <v>348</v>
       </c>
       <c r="N32" t="n">
-        <v>346</v>
+        <v>237.68977056299</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="P32" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q32" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37247,34 +37247,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>121.8861996629213</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>136.2747533519553</v>
       </c>
       <c r="D34" t="n">
-        <v>124.4637819444445</v>
+        <v>123.4637819444445</v>
       </c>
       <c r="E34" t="n">
-        <v>129.0190951630435</v>
+        <v>128.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>135.6171440322581</v>
+        <v>134.6171440322581</v>
       </c>
       <c r="G34" t="n">
-        <v>165.0571107650273</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>182.1267099639552</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>132.2116852152504</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37298,19 +37298,19 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>49.38638914960358</v>
+        <v>6.405909817620905</v>
       </c>
       <c r="T34" t="n">
-        <v>200.4069089035783</v>
+        <v>199.4069089035783</v>
       </c>
       <c r="U34" t="n">
-        <v>36.54339381059363</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>209.8296897837838</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>182.6271901612903</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -37356,22 +37356,22 @@
         <v>28.63682412060302</v>
       </c>
       <c r="L35" t="n">
-        <v>338</v>
+        <v>35.52651256281408</v>
       </c>
       <c r="M35" t="n">
-        <v>263.6203235298445</v>
+        <v>338.0000000000019</v>
       </c>
       <c r="N35" t="n">
-        <v>338</v>
+        <v>338.0000000000019</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>338.0000000000019</v>
       </c>
       <c r="P35" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q35" t="n">
-        <v>338</v>
+        <v>228.0938109670247</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37484,37 +37484,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>125.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>140.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>127.4637819444445</v>
+        <v>102.7564279031092</v>
       </c>
       <c r="E37" t="n">
-        <v>132.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>138.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>168.0571107650273</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>185.1267099639552</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>239.4033968388981</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>136.2116852152504</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.465880038942146</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,19 +37535,19 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>52.38638914960359</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>29.80763773939893</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>186.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>165.5563545698924</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>338</v>
+        <v>338.0000000000092</v>
       </c>
       <c r="K38" t="n">
         <v>28.63682412060302</v>
       </c>
       <c r="L38" t="n">
-        <v>35.52651256281405</v>
+        <v>35.5265125628141</v>
       </c>
       <c r="M38" t="n">
-        <v>228.0938109670304</v>
+        <v>338.0000000000092</v>
       </c>
       <c r="N38" t="n">
-        <v>338</v>
+        <v>338.0000000000092</v>
       </c>
       <c r="O38" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>228.0938109670029</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37724,7 +37724,7 @@
         <v>125.8861996629213</v>
       </c>
       <c r="C40" t="n">
-        <v>140.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>127.4637819444445</v>
@@ -37733,7 +37733,7 @@
         <v>132.0190951630435</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>129.1542799580021</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -37772,25 +37772,25 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>52.38638914960358</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>242.2204896671611</v>
+        <v>262.0471169222634</v>
       </c>
       <c r="V40" t="n">
         <v>213.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>186.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>165.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>125.5346471505376</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>338.0000000000001</v>
+        <v>28.63682412060302</v>
       </c>
       <c r="L41" t="n">
-        <v>35.5265125628141</v>
+        <v>263.6203235297952</v>
       </c>
       <c r="M41" t="n">
-        <v>338</v>
+        <v>338.0000000000164</v>
       </c>
       <c r="N41" t="n">
-        <v>256.7306350876333</v>
+        <v>338.0000000000164</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -37845,7 +37845,7 @@
         <v>32.08628669298693</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>338.0000000000164</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>28.63682412060302</v>
       </c>
       <c r="L44" t="n">
-        <v>35.52651256281405</v>
+        <v>35.52651256281408</v>
       </c>
       <c r="M44" t="n">
-        <v>228.0938109670304</v>
+        <v>338.000000000031</v>
       </c>
       <c r="N44" t="n">
-        <v>338</v>
+        <v>338.000000000031</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>338.000000000031</v>
       </c>
       <c r="P44" t="n">
         <v>32.08628669298693</v>
       </c>
       <c r="Q44" t="n">
-        <v>338</v>
+        <v>228.0938109669374</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
